--- a/Template_Dashboard_v3.xlsx
+++ b/Template_Dashboard_v3.xlsx
@@ -22,11 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="61">
     <font>
@@ -874,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1400,6 +1401,12 @@
     <xf numFmtId="0" fontId="46" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="36" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3992,10 +3999,10 @@
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="B10:F11"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G32:J32"/>
     <mergeCell ref="K8:L9"/>
+    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="G32:J32"/>
     <mergeCell ref="M21:O21"/>
     <mergeCell ref="G5:L5"/>
     <mergeCell ref="B36:W36"/>
@@ -6394,6 +6401,7 @@
   </sheetData>
   <mergeCells count="63">
     <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C55:E55"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="C22:E22"/>
@@ -6445,15 +6453,14 @@
     <mergeCell ref="B121:D121"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="B122:D122"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C73:E73"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="C64:E64"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="C63:E63"/>
   </mergeCells>
@@ -7297,12 +7304,12 @@
           <t>First Shipment</t>
         </is>
       </c>
-      <c r="D67" s="67" t="inlineStr">
+      <c r="D67" s="216" t="inlineStr">
         <is>
           <t>Target (Threshold)</t>
         </is>
       </c>
-      <c r="E67" s="113" t="n">
+      <c r="E67" s="217" t="n">
         <v>46113</v>
       </c>
       <c r="F67" s="114" t="n">
@@ -7372,6 +7379,7 @@
         <v/>
       </c>
     </row>
+    <row r="70"/>
     <row r="71" ht="19.5" customHeight="1" s="132"/>
     <row r="72" ht="15.75" customHeight="1" s="132">
       <c r="C72" s="131" t="inlineStr">

--- a/Template_Dashboard_v3.xlsx
+++ b/Template_Dashboard_v3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7950" yWindow="600" windowWidth="21600" windowHeight="8655" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="61">
     <font>
@@ -422,7 +422,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000066CC"/>
+      <color rgb="FF0066CC"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -651,20 +651,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-        <bgColor rgb="00F0F0F0"/>
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF99"/>
-        <bgColor rgb="00FFFF99"/>
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4E6F3"/>
-        <bgColor rgb="00D4E6F3"/>
+        <fgColor rgb="FFD4E6F3"/>
+        <bgColor rgb="FFD4E6F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -1169,9 +1169,6 @@
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="36" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1203,191 +1200,205 @@
     </xf>
     <xf numFmtId="167" fontId="46" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="36" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="36" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="56" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1396,17 +1407,6 @@
     <xf numFmtId="0" fontId="39" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="38" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="36" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1934,453 +1934,453 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="38" customWidth="1" style="132" min="1" max="1"/>
-    <col width="28" customWidth="1" style="132" min="2" max="2"/>
-    <col width="50" customWidth="1" style="132" min="3" max="3"/>
+    <col width="38" customWidth="1" style="140" min="1" max="1"/>
+    <col width="28" customWidth="1" style="140" min="2" max="2"/>
+    <col width="50" customWidth="1" style="140" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="132">
-      <c r="A1" s="135" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="140">
+      <c r="A1" s="185" t="inlineStr">
         <is>
           <t>KONFIGURASI GLOBAL — PROJECT RISK &amp; HEALTH DASHBOARD</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="136" t="inlineStr">
+      <c r="A2" s="186" t="inlineStr">
         <is>
           <t>Sheet ini adalah pusat pengaturan. Ubah nilai di kolom B untuk menyesuaikan seluruh dashboard (Excel &amp; HTML).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="132">
-      <c r="A4" s="134" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1" s="140">
+      <c r="A4" s="184" t="inlineStr">
         <is>
           <t>A. IDENTITAS PROYEK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="140" t="inlineStr">
+      <c r="A5" s="191" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B5" s="140" t="inlineStr">
+      <c r="B5" s="191" t="inlineStr">
         <is>
           <t>Nilai</t>
         </is>
       </c>
-      <c r="C5" s="140" t="inlineStr">
+      <c r="C5" s="191" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="137" t="inlineStr">
+      <c r="A6" s="187" t="inlineStr">
         <is>
           <t>Nama Perusahaan</t>
         </is>
       </c>
-      <c r="B6" s="117" t="inlineStr">
-        <is>
-          <t>Perusahaan X (Mockup Only)</t>
-        </is>
-      </c>
-      <c r="C6" s="137" t="inlineStr">
+      <c r="B6" s="116" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C6" s="187" t="inlineStr">
         <is>
           <t>Nama lengkap perusahaan pemilik proyek</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="137" t="inlineStr">
+      <c r="A7" s="187" t="inlineStr">
         <is>
           <t>Nama Proyek</t>
         </is>
       </c>
-      <c r="B7" s="117" t="inlineStr">
-        <is>
-          <t>Proyek X</t>
-        </is>
-      </c>
-      <c r="C7" s="137" t="inlineStr">
+      <c r="B7" s="116" t="inlineStr">
+        <is>
+          <t>Satu</t>
+        </is>
+      </c>
+      <c r="C7" s="187" t="inlineStr">
         <is>
           <t>Nama proyek yang dilaporkan</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="137" t="inlineStr">
+      <c r="A8" s="187" t="inlineStr">
         <is>
           <t>Kapasitas Produksi</t>
         </is>
       </c>
-      <c r="B8" s="117" t="inlineStr">
+      <c r="B8" s="116" t="inlineStr">
         <is>
           <t>300.000 MTPY</t>
         </is>
       </c>
-      <c r="C8" s="137" t="inlineStr">
+      <c r="C8" s="187" t="inlineStr">
         <is>
           <t>Kapasitas desain pabrik</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="132">
-      <c r="A10" s="134" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="140">
+      <c r="A10" s="184" t="inlineStr">
         <is>
           <t>B. BOBOT 5 PILAR PROJECT HEALTH SCORE (PHS)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="140" t="inlineStr">
+      <c r="A11" s="191" t="inlineStr">
         <is>
           <t>Pilar Kesehatan</t>
         </is>
       </c>
-      <c r="B11" s="140" t="inlineStr">
+      <c r="B11" s="191" t="inlineStr">
         <is>
           <t>Bobot</t>
         </is>
       </c>
-      <c r="C11" s="140" t="inlineStr">
+      <c r="C11" s="191" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="137" t="inlineStr">
+      <c r="A12" s="187" t="inlineStr">
         <is>
           <t>Financial Health</t>
         </is>
       </c>
-      <c r="B12" s="118" t="n">
+      <c r="B12" s="117" t="n">
         <v>0.2</v>
       </c>
-      <c r="C12" s="137" t="inlineStr">
+      <c r="C12" s="187" t="inlineStr">
         <is>
           <t>Berdasarkan CPI</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="137" t="inlineStr">
+      <c r="A13" s="187" t="inlineStr">
         <is>
           <t>Schedule Health</t>
         </is>
       </c>
-      <c r="B13" s="118" t="n">
+      <c r="B13" s="117" t="n">
         <v>0.2</v>
       </c>
-      <c r="C13" s="137" t="inlineStr">
+      <c r="C13" s="187" t="inlineStr">
         <is>
           <t>Berdasarkan SPI</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="137" t="inlineStr">
+      <c r="A14" s="187" t="inlineStr">
         <is>
           <t>Supply Readiness (SRI)</t>
         </is>
       </c>
-      <c r="B14" s="118" t="n">
+      <c r="B14" s="117" t="n">
         <v>0.2</v>
       </c>
-      <c r="C14" s="137" t="inlineStr">
+      <c r="C14" s="187" t="inlineStr">
         <is>
           <t>Indeks kesiapan pasokan bahan baku</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="137" t="inlineStr">
+      <c r="A15" s="187" t="inlineStr">
         <is>
           <t>Project Execution (PEI)</t>
         </is>
       </c>
-      <c r="B15" s="118" t="n">
+      <c r="B15" s="117" t="n">
         <v>0.2</v>
       </c>
-      <c r="C15" s="137" t="inlineStr">
+      <c r="C15" s="187" t="inlineStr">
         <is>
           <t>Indeks pelaksanaan proyek fisik</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="137" t="inlineStr">
+      <c r="A16" s="187" t="inlineStr">
         <is>
           <t>Commercial Readiness (CRI)</t>
         </is>
       </c>
-      <c r="B16" s="118" t="n">
+      <c r="B16" s="117" t="n">
         <v>0.2</v>
       </c>
-      <c r="C16" s="137" t="inlineStr">
+      <c r="C16" s="187" t="inlineStr">
         <is>
           <t>Indeks kesiapan komersial</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="140" t="inlineStr">
+      <c r="A17" s="191" t="inlineStr">
         <is>
           <t>TOTAL BOBOT</t>
         </is>
       </c>
-      <c r="B17" s="119">
+      <c r="B17" s="118">
         <f>SUM(B12:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="140" t="inlineStr">
+      <c r="C17" s="191" t="inlineStr">
         <is>
           <t>Harus = 1.00</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="132">
-      <c r="A19" s="134" t="inlineStr">
+    <row r="19" ht="15.75" customHeight="1" s="140">
+      <c r="A19" s="184" t="inlineStr">
         <is>
           <t>C. BOBOT OVERALL RISK INDEX</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="140" t="inlineStr">
+      <c r="A20" s="191" t="inlineStr">
         <is>
           <t>Komponen Risiko</t>
         </is>
       </c>
-      <c r="B20" s="140" t="inlineStr">
+      <c r="B20" s="191" t="inlineStr">
         <is>
           <t>Bobot</t>
         </is>
       </c>
-      <c r="C20" s="140" t="inlineStr">
+      <c r="C20" s="191" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="137" t="inlineStr">
+      <c r="A21" s="187" t="inlineStr">
         <is>
           <t>Supply Risk Index</t>
         </is>
       </c>
-      <c r="B21" s="118" t="n">
+      <c r="B21" s="117" t="n">
         <v>0.4</v>
       </c>
-      <c r="C21" s="137" t="inlineStr">
+      <c r="C21" s="187" t="inlineStr">
         <is>
           <t>Bahan baku, logistik</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="137" t="inlineStr">
+      <c r="A22" s="187" t="inlineStr">
         <is>
           <t>Execution Risk Index</t>
         </is>
       </c>
-      <c r="B22" s="118" t="n">
+      <c r="B22" s="117" t="n">
         <v>0.4</v>
       </c>
-      <c r="C22" s="137" t="inlineStr">
+      <c r="C22" s="187" t="inlineStr">
         <is>
           <t>Engineering, procurement, construction</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="137" t="inlineStr">
+      <c r="A23" s="187" t="inlineStr">
         <is>
           <t>Commercial Risk Index</t>
         </is>
       </c>
-      <c r="B23" s="118" t="n">
+      <c r="B23" s="117" t="n">
         <v>0.2</v>
       </c>
-      <c r="C23" s="137" t="inlineStr">
+      <c r="C23" s="187" t="inlineStr">
         <is>
           <t>Offtake, marketing, distribusi</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="140" t="inlineStr">
+      <c r="A24" s="191" t="inlineStr">
         <is>
           <t>TOTAL BOBOT</t>
         </is>
       </c>
-      <c r="B24" s="119">
+      <c r="B24" s="118">
         <f>SUM(B21:B23)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="132">
-      <c r="A26" s="134" t="inlineStr">
+    <row r="26" ht="15.75" customHeight="1" s="140">
+      <c r="A26" s="184" t="inlineStr">
         <is>
           <t>D. PENGATURAN TAMPILAN DASHBOARD</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="140" t="inlineStr">
+      <c r="A27" s="191" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B27" s="140" t="inlineStr">
+      <c r="B27" s="191" t="inlineStr">
         <is>
           <t>Nilai</t>
         </is>
       </c>
-      <c r="C27" s="140" t="inlineStr">
+      <c r="C27" s="191" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="137" t="inlineStr">
+      <c r="A28" s="187" t="inlineStr">
         <is>
           <t>Jumlah Executive Actions</t>
         </is>
       </c>
-      <c r="B28" s="117" t="n">
+      <c r="B28" s="116" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="137" t="inlineStr">
+      <c r="C28" s="187" t="inlineStr">
         <is>
           <t>Berapa prioritas action yang ditampilkan di slide</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="137" t="inlineStr">
+      <c r="A29" s="187" t="inlineStr">
         <is>
           <t>EWS Buffer Toleransi (%)</t>
         </is>
       </c>
-      <c r="B29" s="117" t="n">
+      <c r="B29" s="116" t="n">
         <v>10</v>
       </c>
-      <c r="C29" s="137" t="inlineStr">
+      <c r="C29" s="187" t="inlineStr">
         <is>
           <t>Persentase buffer batas Waspada</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="132">
-      <c r="A31" s="134" t="inlineStr">
+    <row r="31" ht="15.75" customHeight="1" s="140">
+      <c r="A31" s="184" t="inlineStr">
         <is>
           <t>E. KUSTOMISASI WARNA (HEX CODE)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="140" t="inlineStr">
+      <c r="A32" s="191" t="inlineStr">
         <is>
           <t>Elemen</t>
         </is>
       </c>
-      <c r="B32" s="140" t="inlineStr">
+      <c r="B32" s="191" t="inlineStr">
         <is>
           <t>Hex Code</t>
         </is>
       </c>
-      <c r="C32" s="140" t="inlineStr">
+      <c r="C32" s="191" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="137" t="inlineStr">
+      <c r="A33" s="187" t="inlineStr">
         <is>
           <t>Warna Hijau (Aman)</t>
         </is>
       </c>
-      <c r="B33" s="117" t="inlineStr">
+      <c r="B33" s="116" t="inlineStr">
         <is>
           <t>#2E9B57</t>
         </is>
       </c>
-      <c r="C33" s="120" t="inlineStr">
+      <c r="C33" s="119" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="137" t="inlineStr">
+      <c r="A34" s="187" t="inlineStr">
         <is>
           <t>Warna Kuning (Pantau)</t>
         </is>
       </c>
-      <c r="B34" s="117" t="inlineStr">
+      <c r="B34" s="116" t="inlineStr">
         <is>
           <t>#E8B93A</t>
         </is>
       </c>
-      <c r="C34" s="121" t="inlineStr">
+      <c r="C34" s="120" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="137" t="inlineStr">
+      <c r="A35" s="187" t="inlineStr">
         <is>
           <t>Warna Oranye (Waspada)</t>
         </is>
       </c>
-      <c r="B35" s="117" t="inlineStr">
+      <c r="B35" s="116" t="inlineStr">
         <is>
           <t>#E4622E</t>
         </is>
       </c>
-      <c r="C35" s="122" t="inlineStr">
+      <c r="C35" s="121" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="137" t="inlineStr">
+      <c r="A36" s="187" t="inlineStr">
         <is>
           <t>Warna Merah (Kritis)</t>
         </is>
       </c>
-      <c r="B36" s="117" t="inlineStr">
+      <c r="B36" s="116" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
       </c>
-      <c r="C36" s="123" t="inlineStr">
+      <c r="C36" s="122" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="137" t="inlineStr">
+      <c r="A37" s="187" t="inlineStr">
         <is>
           <t>Warna Navy (Aksen)</t>
         </is>
       </c>
-      <c r="B37" s="117" t="inlineStr">
+      <c r="B37" s="116" t="inlineStr">
         <is>
           <t>#0B1F3A</t>
         </is>
       </c>
-      <c r="C37" s="124" t="inlineStr">
+      <c r="C37" s="123" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
@@ -2409,316 +2409,316 @@
   <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="22" customWidth="1" style="132" min="1" max="1"/>
-    <col width="14" customWidth="1" style="132" min="2" max="8"/>
+    <col width="22" customWidth="1" style="140" min="1" max="1"/>
+    <col width="14" customWidth="1" style="140" min="2" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="132">
-      <c r="A1" s="139" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="140">
+      <c r="A1" s="190" t="inlineStr">
         <is>
           <t>PANDUAN PENGGUNAAN — PROJECT RISK &amp; HEALTH DASHBOARD v3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="136" t="inlineStr">
+      <c r="A2" s="186" t="inlineStr">
         <is>
           <t>Versi 3.0 | Dibuat untuk memudahkan pelaporan risiko dan kesehatan proyek secara berkala.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="132">
-      <c r="A4" s="134" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1" s="140">
+      <c r="A4" s="184" t="inlineStr">
         <is>
           <t>1. PENDAHULUAN</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="137" t="inlineStr">
+      <c r="A5" s="187" t="inlineStr">
         <is>
           <t>Dashboard ini dirancang untuk memantau kesehatan proyek melalui 5 pilar utama:</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="137" t="inlineStr">
+      <c r="A6" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  a. Financial Health (CPI &amp; SPI) — efisiensi biaya dan jadwal</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="137" t="inlineStr">
+      <c r="A7" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  b. Supply Readiness Index (SRI) — kesiapan pasokan bahan baku</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="137" t="inlineStr">
+      <c r="A8" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  c. Project Execution Index (PEI) — pelaksanaan proyek fisik</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="137" t="inlineStr">
+      <c r="A9" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  d. Commercial Readiness Index (CRI) — kesiapan komersial</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="137" t="inlineStr">
+      <c r="A10" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  e. Risk Index — profil risiko keseluruhan (benchmark Pertamina)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="132">
-      <c r="A12" s="134" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1" s="140">
+      <c r="A12" s="184" t="inlineStr">
         <is>
           <t>2. STRUKTUR FILE EXCEL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="140" t="inlineStr">
+      <c r="A13" s="191" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C13" s="140" t="inlineStr">
+      <c r="C13" s="191" t="inlineStr">
         <is>
           <t>Fungsi</t>
         </is>
       </c>
-      <c r="F13" s="140" t="inlineStr">
+      <c r="F13" s="191" t="inlineStr">
         <is>
           <t>Siapa Mengisi</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="138" t="inlineStr">
+      <c r="A14" s="189" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="C14" s="137" t="inlineStr">
+      <c r="C14" s="187" t="inlineStr">
         <is>
           <t>Pengaturan global: nama proyek, bobot pilar, warna</t>
         </is>
       </c>
-      <c r="F14" s="137" t="inlineStr">
+      <c r="F14" s="187" t="inlineStr">
         <is>
           <t>PM / PMO (sekali)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="138" t="inlineStr">
+      <c r="A15" s="189" t="inlineStr">
         <is>
           <t>Panduan</t>
         </is>
       </c>
-      <c r="C15" s="137" t="inlineStr">
+      <c r="C15" s="187" t="inlineStr">
         <is>
           <t>Manual penggunaan (sheet ini)</t>
         </is>
       </c>
-      <c r="F15" s="137" t="inlineStr">
+      <c r="F15" s="187" t="inlineStr">
         <is>
           <t>Hanya dibaca</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="138" t="inlineStr">
+      <c r="A16" s="189" t="inlineStr">
         <is>
           <t>Referensi_Threshold</t>
         </is>
       </c>
-      <c r="C16" s="137" t="inlineStr">
+      <c r="C16" s="187" t="inlineStr">
         <is>
           <t>Referensi formula, threshold, skala risiko</t>
         </is>
       </c>
-      <c r="F16" s="137" t="inlineStr">
+      <c r="F16" s="187" t="inlineStr">
         <is>
           <t>Risk Manager (sekali)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="138" t="inlineStr">
+      <c r="A17" s="189" t="inlineStr">
         <is>
           <t>Input_Bulanan</t>
         </is>
       </c>
-      <c r="C17" s="137" t="inlineStr">
+      <c r="C17" s="187" t="inlineStr">
         <is>
           <t>Input data utama setiap bulan</t>
         </is>
       </c>
-      <c r="F17" s="137" t="inlineStr">
+      <c r="F17" s="187" t="inlineStr">
         <is>
           <t>Project Control (bulanan)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="138" t="inlineStr">
+      <c r="A18" s="189" t="inlineStr">
         <is>
           <t>Risk_Action_Tracker</t>
         </is>
       </c>
-      <c r="C18" s="137" t="inlineStr">
+      <c r="C18" s="187" t="inlineStr">
         <is>
           <t>Tracker aksi mitigasi &amp; keputusan Direksi</t>
         </is>
       </c>
-      <c r="F18" s="137" t="inlineStr">
+      <c r="F18" s="187" t="inlineStr">
         <is>
           <t>Project Control (bulanan)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="138" t="inlineStr">
+      <c r="A19" s="189" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="C19" s="137" t="inlineStr">
+      <c r="C19" s="187" t="inlineStr">
         <is>
           <t>Ringkasan visual otomatis</t>
         </is>
       </c>
-      <c r="F19" s="137" t="inlineStr">
+      <c r="F19" s="187" t="inlineStr">
         <is>
           <t>Otomatis</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="132">
-      <c r="A21" s="134" t="inlineStr">
+    <row r="21" ht="15.75" customHeight="1" s="140">
+      <c r="A21" s="184" t="inlineStr">
         <is>
           <t>3. PANDUAN WARNA SEL</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="117" t="inlineStr">
+      <c r="A22" s="116" t="inlineStr">
         <is>
           <t>KUNING (font biru)</t>
         </is>
       </c>
-      <c r="B22" s="137" t="inlineStr">
+      <c r="B22" s="187" t="inlineStr">
         <is>
           <t>Isi data Anda di sini</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="140" t="inlineStr">
+      <c r="A23" s="191" t="inlineStr">
         <is>
           <t>ABU-ABU</t>
         </is>
       </c>
-      <c r="B23" s="137" t="inlineStr">
+      <c r="B23" s="187" t="inlineStr">
         <is>
           <t>Jangan diubah manual</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="132">
-      <c r="A26" s="134" t="inlineStr">
+    <row r="26" ht="15.75" customHeight="1" s="140">
+      <c r="A26" s="184" t="inlineStr">
         <is>
           <t>4. MENAMBAH BARIS BARU (EWS / TOP RISK / ACTIONS)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="137" t="inlineStr">
+      <c r="A27" s="187" t="inlineStr">
         <is>
           <t>Untuk menambah parameter EWS atau Top Risk baru:</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="137" t="inlineStr">
+      <c r="A28" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  a. Klik kanan pada baris TERAKHIR data di bagian tersebut</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="137" t="inlineStr">
+      <c r="A29" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  b. Pilih 'Insert' -&gt; 'Entire Row' untuk menyisipkan baris baru</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="137" t="inlineStr">
+      <c r="A30" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  c. Salin formula dari baris di atas (khusus kolom formula/abu-abu)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="137" t="inlineStr">
+      <c r="A31" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  d. Isi data baru di kolom input (kuning)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="137" t="inlineStr">
+      <c r="A32" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  e. HTML importer akan otomatis mendeteksi baris baru saat import</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="132">
-      <c r="A34" s="134" t="inlineStr">
+    <row r="34" ht="15.75" customHeight="1" s="140">
+      <c r="A34" s="184" t="inlineStr">
         <is>
           <t>5. MENGUBAH BOBOT</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="137" t="inlineStr">
+      <c r="A35" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  a. Buka sheet 'Referensi_Threshold' untuk bobot SRI/PEI/CRI</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="137" t="inlineStr">
+      <c r="A36" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  b. Ubah nilai bobot di kolom B</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="137" t="inlineStr">
+      <c r="A37" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  c. Sheet 'Input_Bulanan' kolom E otomatis menyesuaikan</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="213" t="inlineStr">
+      <c r="A38" s="188" t="inlineStr">
         <is>
           <t>5. CARA MENGATUR PRIORITAS EXECUTIVE ACTIONS</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="137" t="inlineStr">
+      <c r="A39" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  a. Buka sheet 'Risk_Action_Tracker'</t>
         </is>
@@ -2738,50 +2738,50 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="132">
-      <c r="A42" s="134" t="inlineStr">
+    <row r="42" ht="15.75" customHeight="1" s="140">
+      <c r="A42" s="184" t="inlineStr">
         <is>
           <t xml:space="preserve">  d. Untuk menyembunyikan aksi dari slide utama, dikosongkan atau diisi angka 0.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="137" t="inlineStr">
+      <c r="A43" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  a. Buka file html</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="137" t="inlineStr">
+      <c r="A44" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  b. Klik tombol 'Muat Data Excel' di toolbar atas</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="137" t="inlineStr">
+      <c r="A45" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  c. Pilih file Excel yang sudah diisi</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="137" t="inlineStr">
+      <c r="A46" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  d. Dashboard akan otomatis memperbarui semua panel</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="137" t="inlineStr">
+      <c r="A47" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  e. Gunakan tombol PNG/JPG/PDF untuk mengekspor slide</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="137" t="inlineStr">
+      <c r="A48" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve">  f. Gunakan tombol Dark Mode untuk mode malam</t>
         </is>
@@ -2806,10 +2806,10 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A26:H26"/>
@@ -2822,19 +2822,19 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="B23:H23"/>
-    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A19:B19"/>
@@ -2844,7 +2844,7 @@
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2860,149 +2860,149 @@
   <dimension ref="B1:W37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="1.53125" customWidth="1" style="132" min="1" max="1"/>
-    <col width="7.265625" customWidth="1" style="132" min="2" max="13"/>
-    <col width="14.06640625" bestFit="1" customWidth="1" style="132" min="14" max="14"/>
-    <col width="7.265625" customWidth="1" style="132" min="15" max="23"/>
+    <col width="1.53125" customWidth="1" style="140" min="1" max="1"/>
+    <col width="7.265625" customWidth="1" style="140" min="2" max="13"/>
+    <col width="14.06640625" bestFit="1" customWidth="1" style="140" min="14" max="14"/>
+    <col width="7.265625" customWidth="1" style="140" min="15" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="132">
-      <c r="B1" s="163" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="140">
+      <c r="B1" s="174" t="inlineStr">
         <is>
           <t>PROJECT RISK &amp; HEALTH DASHBOARD  -  Proyek X PROJECT  Perusahaan X (Perusahaan X)</t>
         </is>
       </c>
-      <c r="C1" s="142" t="n"/>
-      <c r="D1" s="142" t="n"/>
-      <c r="E1" s="142" t="n"/>
-      <c r="F1" s="142" t="n"/>
-      <c r="G1" s="142" t="n"/>
-      <c r="H1" s="142" t="n"/>
-      <c r="I1" s="142" t="n"/>
-      <c r="J1" s="142" t="n"/>
-      <c r="K1" s="142" t="n"/>
-      <c r="L1" s="142" t="n"/>
-      <c r="M1" s="142" t="n"/>
-      <c r="N1" s="142" t="n"/>
-      <c r="O1" s="142" t="n"/>
-      <c r="P1" s="142" t="n"/>
-      <c r="Q1" s="142" t="n"/>
-      <c r="R1" s="142" t="n"/>
-      <c r="S1" s="142" t="n"/>
-      <c r="T1" s="142" t="n"/>
-      <c r="U1" s="142" t="n"/>
-      <c r="V1" s="142" t="n"/>
-      <c r="W1" s="143" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="132">
-      <c r="B2" s="184">
-        <f>"Reporting Period: "&amp;Input_Bulanan!D5&amp;"   |   Status: "&amp;Input_Bulanan!F5&amp;"   |   Dicetak: "&amp;TEXT(TODAY(),"DD-MM-YYYY")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1" s="132"/>
-    <row r="4" ht="19.5" customHeight="1" s="132">
-      <c r="B4" s="141" t="inlineStr">
+      <c r="C1" s="136" t="n"/>
+      <c r="D1" s="136" t="n"/>
+      <c r="E1" s="136" t="n"/>
+      <c r="F1" s="136" t="n"/>
+      <c r="G1" s="136" t="n"/>
+      <c r="H1" s="136" t="n"/>
+      <c r="I1" s="136" t="n"/>
+      <c r="J1" s="136" t="n"/>
+      <c r="K1" s="136" t="n"/>
+      <c r="L1" s="136" t="n"/>
+      <c r="M1" s="136" t="n"/>
+      <c r="N1" s="136" t="n"/>
+      <c r="O1" s="136" t="n"/>
+      <c r="P1" s="136" t="n"/>
+      <c r="Q1" s="136" t="n"/>
+      <c r="R1" s="136" t="n"/>
+      <c r="S1" s="136" t="n"/>
+      <c r="T1" s="136" t="n"/>
+      <c r="U1" s="136" t="n"/>
+      <c r="V1" s="136" t="n"/>
+      <c r="W1" s="137" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="140">
+      <c r="B2" s="152">
+        <f>"Reporting Period: "&amp;TEXT(Input_Bulanan!D5, "mmmm yyyy")&amp;"   |   Status: "&amp;Input_Bulanan!F5&amp;"   |   Dicetak: "&amp;TEXT(TODAY(), "DD-MM-YYYY")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1" s="140"/>
+    <row r="4" ht="19.5" customHeight="1" s="140">
+      <c r="B4" s="153" t="inlineStr">
         <is>
           <t>PANEL A - PROJECT HEALTH OVERVIEW (Retrospective Performance)</t>
         </is>
       </c>
-      <c r="C4" s="142" t="n"/>
-      <c r="D4" s="142" t="n"/>
-      <c r="E4" s="142" t="n"/>
-      <c r="F4" s="142" t="n"/>
-      <c r="G4" s="142" t="n"/>
-      <c r="H4" s="142" t="n"/>
-      <c r="I4" s="142" t="n"/>
-      <c r="J4" s="142" t="n"/>
-      <c r="K4" s="142" t="n"/>
-      <c r="L4" s="143" t="n"/>
-      <c r="M4" s="141" t="inlineStr">
+      <c r="C4" s="136" t="n"/>
+      <c r="D4" s="136" t="n"/>
+      <c r="E4" s="136" t="n"/>
+      <c r="F4" s="136" t="n"/>
+      <c r="G4" s="136" t="n"/>
+      <c r="H4" s="136" t="n"/>
+      <c r="I4" s="136" t="n"/>
+      <c r="J4" s="136" t="n"/>
+      <c r="K4" s="136" t="n"/>
+      <c r="L4" s="137" t="n"/>
+      <c r="M4" s="153" t="inlineStr">
         <is>
           <t>PANEL B - CURRENT RISK EXPOSURE (Prospective Threats)</t>
         </is>
       </c>
-      <c r="N4" s="142" t="n"/>
-      <c r="O4" s="142" t="n"/>
-      <c r="P4" s="142" t="n"/>
-      <c r="Q4" s="142" t="n"/>
-      <c r="R4" s="142" t="n"/>
-      <c r="S4" s="142" t="n"/>
-      <c r="T4" s="142" t="n"/>
-      <c r="U4" s="142" t="n"/>
-      <c r="V4" s="142" t="n"/>
-      <c r="W4" s="143" t="n"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" s="132">
-      <c r="B5" s="157" t="inlineStr">
+      <c r="N4" s="136" t="n"/>
+      <c r="O4" s="136" t="n"/>
+      <c r="P4" s="136" t="n"/>
+      <c r="Q4" s="136" t="n"/>
+      <c r="R4" s="136" t="n"/>
+      <c r="S4" s="136" t="n"/>
+      <c r="T4" s="136" t="n"/>
+      <c r="U4" s="136" t="n"/>
+      <c r="V4" s="136" t="n"/>
+      <c r="W4" s="137" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="140">
+      <c r="B5" s="162" t="inlineStr">
         <is>
           <t>Overall Project Health Score (PHS)</t>
         </is>
       </c>
-      <c r="C5" s="142" t="n"/>
-      <c r="D5" s="142" t="n"/>
-      <c r="E5" s="142" t="n"/>
-      <c r="F5" s="143" t="n"/>
-      <c r="G5" s="157" t="inlineStr">
+      <c r="C5" s="136" t="n"/>
+      <c r="D5" s="136" t="n"/>
+      <c r="E5" s="136" t="n"/>
+      <c r="F5" s="137" t="n"/>
+      <c r="G5" s="162" t="inlineStr">
         <is>
           <t>Sub-Index Readiness &amp; Performance</t>
         </is>
       </c>
-      <c r="H5" s="142" t="n"/>
-      <c r="I5" s="142" t="n"/>
-      <c r="J5" s="142" t="n"/>
-      <c r="K5" s="142" t="n"/>
-      <c r="L5" s="143" t="n"/>
-      <c r="M5" s="157" t="inlineStr">
+      <c r="H5" s="136" t="n"/>
+      <c r="I5" s="136" t="n"/>
+      <c r="J5" s="136" t="n"/>
+      <c r="K5" s="136" t="n"/>
+      <c r="L5" s="137" t="n"/>
+      <c r="M5" s="162" t="inlineStr">
         <is>
           <t>Overall Risk Level (Composite)</t>
         </is>
       </c>
-      <c r="N5" s="142" t="n"/>
-      <c r="O5" s="142" t="n"/>
-      <c r="P5" s="142" t="n"/>
-      <c r="Q5" s="143" t="n"/>
-      <c r="R5" s="187" t="inlineStr">
+      <c r="N5" s="136" t="n"/>
+      <c r="O5" s="136" t="n"/>
+      <c r="P5" s="136" t="n"/>
+      <c r="Q5" s="137" t="n"/>
+      <c r="R5" s="147" t="inlineStr">
         <is>
           <t>Risk Profile Heat Map (Likelihood x Consequence)</t>
         </is>
       </c>
-      <c r="S5" s="142" t="n"/>
-      <c r="T5" s="142" t="n"/>
-      <c r="U5" s="142" t="n"/>
-      <c r="V5" s="142" t="n"/>
-      <c r="W5" s="143" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" s="132">
-      <c r="B6" s="181">
+      <c r="S5" s="136" t="n"/>
+      <c r="T5" s="136" t="n"/>
+      <c r="U5" s="136" t="n"/>
+      <c r="V5" s="136" t="n"/>
+      <c r="W5" s="137" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="140">
+      <c r="B6" s="183">
         <f>((IF(Input_Bulanan!D12&gt;=1,100,Input_Bulanan!D12*100)*0.2)+(IF(Input_Bulanan!D14&gt;=1,100,Input_Bulanan!D14*100)*0.2)+(Input_Bulanan!D24*100*0.2)+(Input_Bulanan!D32*100*0.2)+(Input_Bulanan!D42*100*0.2))/100</f>
         <v/>
       </c>
-      <c r="C6" s="147" t="n"/>
-      <c r="D6" s="147" t="n"/>
-      <c r="E6" s="147" t="n"/>
-      <c r="F6" s="148" t="n"/>
-      <c r="G6" s="174" t="inlineStr">
+      <c r="C6" s="156" t="n"/>
+      <c r="D6" s="156" t="n"/>
+      <c r="E6" s="156" t="n"/>
+      <c r="F6" s="142" t="n"/>
+      <c r="G6" s="160" t="inlineStr">
         <is>
           <t>Supply Readiness Index (SRI)</t>
         </is>
       </c>
-      <c r="H6" s="147" t="n"/>
-      <c r="I6" s="147" t="n"/>
-      <c r="J6" s="147" t="n"/>
-      <c r="K6" s="154">
+      <c r="H6" s="156" t="n"/>
+      <c r="I6" s="156" t="n"/>
+      <c r="J6" s="156" t="n"/>
+      <c r="K6" s="141">
         <f>Input_Bulanan!D24</f>
         <v/>
       </c>
-      <c r="L6" s="148" t="n"/>
-      <c r="M6" s="185">
+      <c r="L6" s="142" t="n"/>
+      <c r="M6" s="155">
         <f>Input_Bulanan!D49</f>
         <v/>
       </c>
-      <c r="N6" s="147" t="n"/>
-      <c r="O6" s="147" t="n"/>
-      <c r="P6" s="147" t="n"/>
-      <c r="Q6" s="148" t="n"/>
+      <c r="N6" s="156" t="n"/>
+      <c r="O6" s="156" t="n"/>
+      <c r="P6" s="156" t="n"/>
+      <c r="Q6" s="142" t="n"/>
       <c r="R6" s="1" t="inlineStr">
         <is>
           <t>L=5</t>
@@ -3029,17 +3029,17 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="132">
-      <c r="B7" s="178" t="n"/>
-      <c r="F7" s="179" t="n"/>
-      <c r="G7" s="149" t="n"/>
-      <c r="H7" s="150" t="n"/>
-      <c r="I7" s="150" t="n"/>
-      <c r="J7" s="150" t="n"/>
-      <c r="K7" s="150" t="n"/>
-      <c r="L7" s="151" t="n"/>
-      <c r="M7" s="178" t="n"/>
-      <c r="Q7" s="179" t="n"/>
+    <row r="7" ht="15.75" customHeight="1" s="140">
+      <c r="B7" s="157" t="n"/>
+      <c r="F7" s="158" t="n"/>
+      <c r="G7" s="159" t="n"/>
+      <c r="H7" s="143" t="n"/>
+      <c r="I7" s="143" t="n"/>
+      <c r="J7" s="143" t="n"/>
+      <c r="K7" s="143" t="n"/>
+      <c r="L7" s="144" t="n"/>
+      <c r="M7" s="157" t="n"/>
+      <c r="Q7" s="158" t="n"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
           <t>L=4</t>
@@ -3066,24 +3066,24 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="132">
-      <c r="B8" s="178" t="n"/>
-      <c r="F8" s="179" t="n"/>
-      <c r="G8" s="174" t="inlineStr">
+    <row r="8" ht="15.75" customHeight="1" s="140">
+      <c r="B8" s="157" t="n"/>
+      <c r="F8" s="158" t="n"/>
+      <c r="G8" s="160" t="inlineStr">
         <is>
           <t>Project Execution Index (PEI)</t>
         </is>
       </c>
-      <c r="H8" s="147" t="n"/>
-      <c r="I8" s="147" t="n"/>
-      <c r="J8" s="147" t="n"/>
-      <c r="K8" s="154">
+      <c r="H8" s="156" t="n"/>
+      <c r="I8" s="156" t="n"/>
+      <c r="J8" s="156" t="n"/>
+      <c r="K8" s="141">
         <f>Input_Bulanan!D32</f>
         <v/>
       </c>
-      <c r="L8" s="148" t="n"/>
-      <c r="M8" s="178" t="n"/>
-      <c r="Q8" s="179" t="n"/>
+      <c r="L8" s="142" t="n"/>
+      <c r="M8" s="157" t="n"/>
+      <c r="Q8" s="158" t="n"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
           <t>L=3</t>
@@ -3110,23 +3110,23 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="132">
-      <c r="B9" s="149" t="n"/>
-      <c r="C9" s="150" t="n"/>
-      <c r="D9" s="150" t="n"/>
-      <c r="E9" s="150" t="n"/>
-      <c r="F9" s="151" t="n"/>
-      <c r="G9" s="149" t="n"/>
-      <c r="H9" s="150" t="n"/>
-      <c r="I9" s="150" t="n"/>
-      <c r="J9" s="150" t="n"/>
-      <c r="K9" s="150" t="n"/>
-      <c r="L9" s="151" t="n"/>
-      <c r="M9" s="149" t="n"/>
-      <c r="N9" s="150" t="n"/>
-      <c r="O9" s="150" t="n"/>
-      <c r="P9" s="150" t="n"/>
-      <c r="Q9" s="151" t="n"/>
+    <row r="9" ht="15.75" customHeight="1" s="140">
+      <c r="B9" s="159" t="n"/>
+      <c r="C9" s="143" t="n"/>
+      <c r="D9" s="143" t="n"/>
+      <c r="E9" s="143" t="n"/>
+      <c r="F9" s="144" t="n"/>
+      <c r="G9" s="159" t="n"/>
+      <c r="H9" s="143" t="n"/>
+      <c r="I9" s="143" t="n"/>
+      <c r="J9" s="143" t="n"/>
+      <c r="K9" s="143" t="n"/>
+      <c r="L9" s="144" t="n"/>
+      <c r="M9" s="159" t="n"/>
+      <c r="N9" s="143" t="n"/>
+      <c r="O9" s="143" t="n"/>
+      <c r="P9" s="143" t="n"/>
+      <c r="Q9" s="144" t="n"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
           <t>L=2</t>
@@ -3153,36 +3153,36 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="132">
-      <c r="B10" s="146">
+    <row r="10" ht="15.75" customHeight="1" s="140">
+      <c r="B10" s="182">
         <f>IF(B6&gt;=0.9,"HIJAU - SEHAT",IF(B6&gt;=0.75,"KUNING - PANTAU",IF(B6&gt;=0.6,"ORANYE - WASPADA","MERAH - KRITIS")))</f>
         <v/>
       </c>
-      <c r="C10" s="147" t="n"/>
-      <c r="D10" s="147" t="n"/>
-      <c r="E10" s="147" t="n"/>
-      <c r="F10" s="148" t="n"/>
-      <c r="G10" s="174" t="inlineStr">
+      <c r="C10" s="156" t="n"/>
+      <c r="D10" s="156" t="n"/>
+      <c r="E10" s="156" t="n"/>
+      <c r="F10" s="142" t="n"/>
+      <c r="G10" s="160" t="inlineStr">
         <is>
           <t>Commercial Readiness Index (CRI)</t>
         </is>
       </c>
-      <c r="H10" s="147" t="n"/>
-      <c r="I10" s="147" t="n"/>
-      <c r="J10" s="147" t="n"/>
-      <c r="K10" s="154">
+      <c r="H10" s="156" t="n"/>
+      <c r="I10" s="156" t="n"/>
+      <c r="J10" s="156" t="n"/>
+      <c r="K10" s="141">
         <f>Input_Bulanan!D42</f>
         <v/>
       </c>
-      <c r="L10" s="148" t="n"/>
-      <c r="M10" s="176">
+      <c r="L10" s="142" t="n"/>
+      <c r="M10" s="168">
         <f>"Skor Komposit: "&amp;TEXT(Input_Bulanan!D48,"0,00")&amp;" / 100"</f>
         <v/>
       </c>
-      <c r="N10" s="147" t="n"/>
-      <c r="O10" s="147" t="n"/>
-      <c r="P10" s="147" t="n"/>
-      <c r="Q10" s="148" t="n"/>
+      <c r="N10" s="156" t="n"/>
+      <c r="O10" s="156" t="n"/>
+      <c r="P10" s="156" t="n"/>
+      <c r="Q10" s="142" t="n"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
           <t>L=1</t>
@@ -3209,23 +3209,23 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="12" customHeight="1" s="132">
-      <c r="B11" s="149" t="n"/>
-      <c r="C11" s="150" t="n"/>
-      <c r="D11" s="150" t="n"/>
-      <c r="E11" s="150" t="n"/>
-      <c r="F11" s="151" t="n"/>
-      <c r="G11" s="149" t="n"/>
-      <c r="H11" s="150" t="n"/>
-      <c r="I11" s="150" t="n"/>
-      <c r="J11" s="150" t="n"/>
-      <c r="K11" s="150" t="n"/>
-      <c r="L11" s="151" t="n"/>
-      <c r="M11" s="149" t="n"/>
-      <c r="N11" s="150" t="n"/>
-      <c r="O11" s="150" t="n"/>
-      <c r="P11" s="150" t="n"/>
-      <c r="Q11" s="151" t="n"/>
+    <row r="11" ht="12" customHeight="1" s="140">
+      <c r="B11" s="159" t="n"/>
+      <c r="C11" s="143" t="n"/>
+      <c r="D11" s="143" t="n"/>
+      <c r="E11" s="143" t="n"/>
+      <c r="F11" s="144" t="n"/>
+      <c r="G11" s="159" t="n"/>
+      <c r="H11" s="143" t="n"/>
+      <c r="I11" s="143" t="n"/>
+      <c r="J11" s="143" t="n"/>
+      <c r="K11" s="143" t="n"/>
+      <c r="L11" s="144" t="n"/>
+      <c r="M11" s="159" t="n"/>
+      <c r="N11" s="143" t="n"/>
+      <c r="O11" s="143" t="n"/>
+      <c r="P11" s="143" t="n"/>
+      <c r="Q11" s="144" t="n"/>
       <c r="R11" s="7" t="inlineStr">
         <is>
           <t>C -&gt;</t>
@@ -3247,261 +3247,261 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="132">
-      <c r="B12" s="157" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1" s="140">
+      <c r="B12" s="162" t="inlineStr">
         <is>
           <t>Key Financial &amp; Schedule</t>
         </is>
       </c>
-      <c r="C12" s="142" t="n"/>
-      <c r="D12" s="142" t="n"/>
-      <c r="E12" s="142" t="n"/>
-      <c r="F12" s="143" t="n"/>
-      <c r="G12" s="157" t="inlineStr">
+      <c r="C12" s="136" t="n"/>
+      <c r="D12" s="136" t="n"/>
+      <c r="E12" s="136" t="n"/>
+      <c r="F12" s="137" t="n"/>
+      <c r="G12" s="162" t="inlineStr">
         <is>
           <t>Master Schedule S-Curve (USD Juta)</t>
         </is>
       </c>
-      <c r="H12" s="142" t="n"/>
-      <c r="I12" s="142" t="n"/>
-      <c r="J12" s="142" t="n"/>
-      <c r="K12" s="142" t="n"/>
-      <c r="L12" s="143" t="n"/>
-      <c r="M12" s="157" t="inlineStr">
+      <c r="H12" s="136" t="n"/>
+      <c r="I12" s="136" t="n"/>
+      <c r="J12" s="136" t="n"/>
+      <c r="K12" s="136" t="n"/>
+      <c r="L12" s="137" t="n"/>
+      <c r="M12" s="162" t="inlineStr">
         <is>
           <t>Risk Register - Risiko Aktif</t>
         </is>
       </c>
-      <c r="N12" s="142" t="n"/>
-      <c r="O12" s="142" t="n"/>
-      <c r="P12" s="142" t="n"/>
-      <c r="Q12" s="143" t="n"/>
-      <c r="R12" s="157" t="inlineStr">
+      <c r="N12" s="136" t="n"/>
+      <c r="O12" s="136" t="n"/>
+      <c r="P12" s="136" t="n"/>
+      <c r="Q12" s="137" t="n"/>
+      <c r="R12" s="162" t="inlineStr">
         <is>
           <t>Legenda Top Risk (C1-C4)</t>
         </is>
       </c>
-      <c r="S12" s="142" t="n"/>
-      <c r="T12" s="142" t="n"/>
-      <c r="U12" s="142" t="n"/>
-      <c r="V12" s="142" t="n"/>
-      <c r="W12" s="143" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" s="132">
-      <c r="B13" s="155" t="inlineStr">
+      <c r="S12" s="136" t="n"/>
+      <c r="T12" s="136" t="n"/>
+      <c r="U12" s="136" t="n"/>
+      <c r="V12" s="136" t="n"/>
+      <c r="W12" s="137" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" s="140">
+      <c r="B13" s="148" t="inlineStr">
         <is>
           <t>Cost Performance Index (CPI)</t>
         </is>
       </c>
-      <c r="C13" s="142" t="n"/>
-      <c r="D13" s="143" t="n"/>
-      <c r="E13" s="169">
+      <c r="C13" s="136" t="n"/>
+      <c r="D13" s="137" t="n"/>
+      <c r="E13" s="165">
         <f>Input_Bulanan!D12</f>
         <v/>
       </c>
-      <c r="F13" s="143" t="n"/>
-      <c r="G13" s="144" t="inlineStr">
+      <c r="F13" s="137" t="n"/>
+      <c r="G13" s="178" t="inlineStr">
         <is>
           <t>Planned Value (PV)</t>
         </is>
       </c>
-      <c r="H13" s="142" t="n"/>
-      <c r="I13" s="143" t="n"/>
-      <c r="J13" s="161">
+      <c r="H13" s="136" t="n"/>
+      <c r="I13" s="137" t="n"/>
+      <c r="J13" s="167">
         <f>Input_Bulanan!D8</f>
         <v/>
       </c>
-      <c r="K13" s="142" t="n"/>
-      <c r="L13" s="143" t="n"/>
-      <c r="M13" s="170" t="inlineStr">
+      <c r="K13" s="136" t="n"/>
+      <c r="L13" s="137" t="n"/>
+      <c r="M13" s="161" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="142" t="n"/>
-      <c r="O13" s="143" t="n"/>
-      <c r="P13" s="160">
+      <c r="N13" s="136" t="n"/>
+      <c r="O13" s="137" t="n"/>
+      <c r="P13" s="179">
         <f>Input_Bulanan!D52</f>
         <v/>
       </c>
-      <c r="Q13" s="143" t="n"/>
-      <c r="R13" s="195">
+      <c r="Q13" s="137" t="n"/>
+      <c r="R13" s="194">
         <f>Input_Bulanan!C75</f>
         <v/>
       </c>
-      <c r="S13" s="159">
+      <c r="S13" s="172">
         <f>Input_Bulanan!D75&amp;"  |  L="&amp;Input_Bulanan!F75&amp;", C="&amp;Input_Bulanan!G75&amp;", Skala="&amp;Input_Bulanan!H75&amp;" -&gt; "&amp;Input_Bulanan!I75</f>
         <v/>
       </c>
-      <c r="T13" s="142" t="n"/>
-      <c r="U13" s="142" t="n"/>
-      <c r="V13" s="142" t="n"/>
-      <c r="W13" s="142" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" s="132">
-      <c r="B14" s="155" t="inlineStr">
+      <c r="T13" s="136" t="n"/>
+      <c r="U13" s="136" t="n"/>
+      <c r="V13" s="136" t="n"/>
+      <c r="W13" s="136" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" s="140">
+      <c r="B14" s="148" t="inlineStr">
         <is>
           <t>Schedule Performance Index (SPI)</t>
         </is>
       </c>
-      <c r="C14" s="142" t="n"/>
-      <c r="D14" s="143" t="n"/>
-      <c r="E14" s="169">
+      <c r="C14" s="136" t="n"/>
+      <c r="D14" s="137" t="n"/>
+      <c r="E14" s="165">
         <f>Input_Bulanan!D14</f>
         <v/>
       </c>
-      <c r="F14" s="143" t="n"/>
-      <c r="G14" s="144" t="inlineStr">
+      <c r="F14" s="137" t="n"/>
+      <c r="G14" s="178" t="inlineStr">
         <is>
           <t>Earned Value (EV)</t>
         </is>
       </c>
-      <c r="H14" s="142" t="n"/>
-      <c r="I14" s="143" t="n"/>
-      <c r="J14" s="161">
+      <c r="H14" s="136" t="n"/>
+      <c r="I14" s="137" t="n"/>
+      <c r="J14" s="167">
         <f>Input_Bulanan!D9</f>
         <v/>
       </c>
-      <c r="K14" s="142" t="n"/>
-      <c r="L14" s="143" t="n"/>
-      <c r="M14" s="170" t="inlineStr">
+      <c r="K14" s="136" t="n"/>
+      <c r="L14" s="137" t="n"/>
+      <c r="M14" s="161" t="inlineStr">
         <is>
           <t>Moderate to High</t>
         </is>
       </c>
-      <c r="N14" s="142" t="n"/>
-      <c r="O14" s="143" t="n"/>
-      <c r="P14" s="177">
+      <c r="N14" s="136" t="n"/>
+      <c r="O14" s="137" t="n"/>
+      <c r="P14" s="170">
         <f>Input_Bulanan!D53</f>
         <v/>
       </c>
-      <c r="Q14" s="143" t="n"/>
-      <c r="R14" s="195">
+      <c r="Q14" s="137" t="n"/>
+      <c r="R14" s="194">
         <f>Input_Bulanan!C76</f>
         <v/>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="172">
         <f>Input_Bulanan!D76&amp;"  |  L="&amp;Input_Bulanan!F76&amp;", C="&amp;Input_Bulanan!G76&amp;", Skala="&amp;Input_Bulanan!H76&amp;" -&gt; "&amp;Input_Bulanan!I76</f>
         <v/>
       </c>
-      <c r="T14" s="142" t="n"/>
-      <c r="U14" s="142" t="n"/>
-      <c r="V14" s="142" t="n"/>
-      <c r="W14" s="142" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" s="132">
-      <c r="B15" s="155" t="inlineStr">
+      <c r="T14" s="136" t="n"/>
+      <c r="U14" s="136" t="n"/>
+      <c r="V14" s="136" t="n"/>
+      <c r="W14" s="136" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="140">
+      <c r="B15" s="148" t="inlineStr">
         <is>
           <t>Cost Variance (CV), USD Juta</t>
         </is>
       </c>
-      <c r="C15" s="142" t="n"/>
-      <c r="D15" s="143" t="n"/>
-      <c r="E15" s="175">
+      <c r="C15" s="136" t="n"/>
+      <c r="D15" s="137" t="n"/>
+      <c r="E15" s="150">
         <f>Input_Bulanan!D13</f>
         <v/>
       </c>
-      <c r="F15" s="143" t="n"/>
-      <c r="G15" s="144" t="inlineStr">
+      <c r="F15" s="137" t="n"/>
+      <c r="G15" s="178" t="inlineStr">
         <is>
           <t>Actual Cost (AC)</t>
         </is>
       </c>
-      <c r="H15" s="142" t="n"/>
-      <c r="I15" s="143" t="n"/>
-      <c r="J15" s="161">
+      <c r="H15" s="136" t="n"/>
+      <c r="I15" s="137" t="n"/>
+      <c r="J15" s="167">
         <f>Input_Bulanan!D10</f>
         <v/>
       </c>
-      <c r="K15" s="142" t="n"/>
-      <c r="L15" s="143" t="n"/>
-      <c r="M15" s="170" t="inlineStr">
+      <c r="K15" s="136" t="n"/>
+      <c r="L15" s="137" t="n"/>
+      <c r="M15" s="161" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="N15" s="142" t="n"/>
-      <c r="O15" s="143" t="n"/>
-      <c r="P15" s="162">
+      <c r="N15" s="136" t="n"/>
+      <c r="O15" s="137" t="n"/>
+      <c r="P15" s="180">
         <f>Input_Bulanan!D54</f>
         <v/>
       </c>
-      <c r="Q15" s="143" t="n"/>
-      <c r="R15" s="195">
+      <c r="Q15" s="137" t="n"/>
+      <c r="R15" s="194">
         <f>Input_Bulanan!C77</f>
         <v/>
       </c>
-      <c r="S15" s="159">
+      <c r="S15" s="172">
         <f>Input_Bulanan!D77&amp;"  |  L="&amp;Input_Bulanan!F77&amp;", C="&amp;Input_Bulanan!G77&amp;", Skala="&amp;Input_Bulanan!H77&amp;" -&gt; "&amp;Input_Bulanan!I77</f>
         <v/>
       </c>
-      <c r="T15" s="142" t="n"/>
-      <c r="U15" s="142" t="n"/>
-      <c r="V15" s="142" t="n"/>
-      <c r="W15" s="142" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="132">
-      <c r="B16" s="155" t="inlineStr">
+      <c r="T15" s="136" t="n"/>
+      <c r="U15" s="136" t="n"/>
+      <c r="V15" s="136" t="n"/>
+      <c r="W15" s="136" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="140">
+      <c r="B16" s="148" t="inlineStr">
         <is>
           <t>Schedule Variance (SV), USD Juta</t>
         </is>
       </c>
-      <c r="C16" s="142" t="n"/>
-      <c r="D16" s="143" t="n"/>
-      <c r="E16" s="175">
+      <c r="C16" s="136" t="n"/>
+      <c r="D16" s="137" t="n"/>
+      <c r="E16" s="150">
         <f>Input_Bulanan!D15</f>
         <v/>
       </c>
-      <c r="F16" s="143" t="n"/>
-      <c r="G16" s="186" t="inlineStr">
+      <c r="F16" s="137" t="n"/>
+      <c r="G16" s="151" t="inlineStr">
         <is>
           <t>(Bar proporsional: lihat conditional formatting / grafik pada versi HTML)</t>
         </is>
       </c>
-      <c r="H16" s="142" t="n"/>
-      <c r="I16" s="142" t="n"/>
-      <c r="J16" s="142" t="n"/>
-      <c r="K16" s="142" t="n"/>
-      <c r="L16" s="143" t="n"/>
-      <c r="M16" s="170" t="inlineStr">
+      <c r="H16" s="136" t="n"/>
+      <c r="I16" s="136" t="n"/>
+      <c r="J16" s="136" t="n"/>
+      <c r="K16" s="136" t="n"/>
+      <c r="L16" s="137" t="n"/>
+      <c r="M16" s="161" t="inlineStr">
         <is>
           <t>Low to Moderate</t>
         </is>
       </c>
-      <c r="N16" s="142" t="n"/>
-      <c r="O16" s="143" t="n"/>
-      <c r="P16" s="182">
+      <c r="N16" s="136" t="n"/>
+      <c r="O16" s="137" t="n"/>
+      <c r="P16" s="145">
         <f>Input_Bulanan!D55</f>
         <v/>
       </c>
-      <c r="Q16" s="143" t="n"/>
-      <c r="R16" s="195">
+      <c r="Q16" s="137" t="n"/>
+      <c r="R16" s="194">
         <f>Input_Bulanan!C78</f>
         <v/>
       </c>
-      <c r="S16" s="159">
+      <c r="S16" s="172">
         <f>Input_Bulanan!D78&amp;"  |  L="&amp;Input_Bulanan!F78&amp;", C="&amp;Input_Bulanan!G78&amp;", Skala="&amp;Input_Bulanan!H78&amp;" -&gt; "&amp;Input_Bulanan!I78</f>
         <v/>
       </c>
-      <c r="T16" s="142" t="n"/>
-      <c r="U16" s="142" t="n"/>
-      <c r="V16" s="142" t="n"/>
-      <c r="W16" s="142" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="132">
+      <c r="T16" s="136" t="n"/>
+      <c r="U16" s="136" t="n"/>
+      <c r="V16" s="136" t="n"/>
+      <c r="W16" s="136" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="140">
       <c r="L17" s="105" t="n"/>
-      <c r="M17" s="170" t="inlineStr">
+      <c r="M17" s="161" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N17" s="142" t="n"/>
-      <c r="O17" s="143" t="n"/>
-      <c r="P17" s="182">
+      <c r="N17" s="136" t="n"/>
+      <c r="O17" s="137" t="n"/>
+      <c r="P17" s="145">
         <f>Input_Bulanan!D56</f>
         <v/>
       </c>
-      <c r="Q17" s="143" t="n"/>
+      <c r="Q17" s="137" t="n"/>
     </row>
     <row r="18">
       <c r="M18" s="104" t="inlineStr">
@@ -3509,167 +3509,167 @@
           <t>Total Risiko Aktif</t>
         </is>
       </c>
-      <c r="N18" s="142" t="n"/>
-      <c r="O18" s="143" t="n"/>
-      <c r="P18" s="188">
+      <c r="N18" s="136" t="n"/>
+      <c r="O18" s="137" t="n"/>
+      <c r="P18" s="149">
         <f>Input_Bulanan!D57</f>
         <v/>
       </c>
-      <c r="Q18" s="143" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="132"/>
-    <row r="20" ht="15" customHeight="1" s="132">
-      <c r="B20" s="171" t="inlineStr">
+      <c r="Q18" s="137" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="140"/>
+    <row r="20" ht="15" customHeight="1" s="140">
+      <c r="B20" s="173" t="inlineStr">
         <is>
           <t>Catatan Metodologi</t>
         </is>
       </c>
-      <c r="C20" s="147" t="n"/>
-      <c r="D20" s="147" t="n"/>
-      <c r="E20" s="147" t="n"/>
-      <c r="F20" s="147" t="n"/>
-      <c r="G20" s="147" t="n"/>
-      <c r="H20" s="147" t="n"/>
-      <c r="I20" s="147" t="n"/>
-      <c r="J20" s="147" t="n"/>
-      <c r="K20" s="147" t="n"/>
-      <c r="L20" s="148" t="n"/>
-      <c r="M20" s="171" t="inlineStr">
+      <c r="C20" s="156" t="n"/>
+      <c r="D20" s="156" t="n"/>
+      <c r="E20" s="156" t="n"/>
+      <c r="F20" s="156" t="n"/>
+      <c r="G20" s="156" t="n"/>
+      <c r="H20" s="156" t="n"/>
+      <c r="I20" s="156" t="n"/>
+      <c r="J20" s="156" t="n"/>
+      <c r="K20" s="156" t="n"/>
+      <c r="L20" s="142" t="n"/>
+      <c r="M20" s="173" t="inlineStr">
         <is>
           <t>Mitigation Health Progress</t>
         </is>
       </c>
-      <c r="N20" s="142" t="n"/>
-      <c r="O20" s="142" t="n"/>
-      <c r="P20" s="142" t="n"/>
-      <c r="Q20" s="143" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="132">
-      <c r="B21" s="178" t="n"/>
-      <c r="L21" s="179" t="n"/>
-      <c r="M21" s="155" t="inlineStr">
+      <c r="N20" s="136" t="n"/>
+      <c r="O20" s="136" t="n"/>
+      <c r="P20" s="136" t="n"/>
+      <c r="Q20" s="137" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="140">
+      <c r="B21" s="157" t="n"/>
+      <c r="L21" s="158" t="n"/>
+      <c r="M21" s="148" t="inlineStr">
         <is>
           <t>Completed Mitigations</t>
         </is>
       </c>
-      <c r="N21" s="142" t="n"/>
-      <c r="O21" s="143" t="n"/>
-      <c r="P21" s="156">
+      <c r="N21" s="136" t="n"/>
+      <c r="O21" s="137" t="n"/>
+      <c r="P21" s="163">
         <f>Input_Bulanan!D60</f>
         <v/>
       </c>
-      <c r="Q21" s="143" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="132">
-      <c r="B22" s="178" t="n"/>
-      <c r="L22" s="179" t="n"/>
-      <c r="M22" s="155" t="inlineStr">
+      <c r="Q21" s="137" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="140">
+      <c r="B22" s="157" t="n"/>
+      <c r="L22" s="158" t="n"/>
+      <c r="M22" s="148" t="inlineStr">
         <is>
           <t>On Track Mitigations</t>
         </is>
       </c>
-      <c r="N22" s="142" t="n"/>
-      <c r="O22" s="143" t="n"/>
-      <c r="P22" s="156">
+      <c r="N22" s="136" t="n"/>
+      <c r="O22" s="137" t="n"/>
+      <c r="P22" s="163">
         <f>Input_Bulanan!D61</f>
         <v/>
       </c>
-      <c r="Q22" s="143" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="132">
-      <c r="B23" s="178" t="n"/>
-      <c r="L23" s="179" t="n"/>
-      <c r="M23" s="155" t="inlineStr">
+      <c r="Q22" s="137" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="140">
+      <c r="B23" s="157" t="n"/>
+      <c r="L23" s="158" t="n"/>
+      <c r="M23" s="148" t="inlineStr">
         <is>
           <t>Overdue Actions</t>
         </is>
       </c>
-      <c r="N23" s="142" t="n"/>
-      <c r="O23" s="143" t="n"/>
-      <c r="P23" s="156">
+      <c r="N23" s="136" t="n"/>
+      <c r="O23" s="137" t="n"/>
+      <c r="P23" s="163">
         <f>Input_Bulanan!D62</f>
         <v/>
       </c>
-      <c r="Q23" s="143" t="n"/>
-    </row>
-    <row r="24" ht="14.25" customHeight="1" s="132">
-      <c r="B24" s="149" t="n"/>
-      <c r="C24" s="150" t="n"/>
-      <c r="D24" s="150" t="n"/>
-      <c r="E24" s="150" t="n"/>
-      <c r="F24" s="150" t="n"/>
-      <c r="G24" s="150" t="n"/>
-      <c r="H24" s="150" t="n"/>
-      <c r="I24" s="150" t="n"/>
-      <c r="J24" s="150" t="n"/>
-      <c r="K24" s="150" t="n"/>
-      <c r="L24" s="151" t="n"/>
-      <c r="M24" s="155" t="inlineStr">
+      <c r="Q23" s="137" t="n"/>
+    </row>
+    <row r="24" ht="14.25" customHeight="1" s="140">
+      <c r="B24" s="159" t="n"/>
+      <c r="C24" s="143" t="n"/>
+      <c r="D24" s="143" t="n"/>
+      <c r="E24" s="143" t="n"/>
+      <c r="F24" s="143" t="n"/>
+      <c r="G24" s="143" t="n"/>
+      <c r="H24" s="143" t="n"/>
+      <c r="I24" s="143" t="n"/>
+      <c r="J24" s="143" t="n"/>
+      <c r="K24" s="143" t="n"/>
+      <c r="L24" s="144" t="n"/>
+      <c r="M24" s="148" t="inlineStr">
         <is>
           <t>Need Escalation (jumlah aksi)</t>
         </is>
       </c>
-      <c r="N24" s="142" t="n"/>
-      <c r="O24" s="143" t="n"/>
-      <c r="P24" s="164">
+      <c r="N24" s="136" t="n"/>
+      <c r="O24" s="137" t="n"/>
+      <c r="P24" s="175">
         <f>Input_Bulanan!D63</f>
         <v/>
       </c>
-      <c r="Q24" s="143" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" s="132"/>
-    <row r="26" ht="15.75" customHeight="1" s="132">
-      <c r="B26" s="173" t="inlineStr">
+      <c r="Q24" s="137" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="140"/>
+    <row r="26" ht="15.75" customHeight="1" s="140">
+      <c r="B26" s="166" t="inlineStr">
         <is>
           <t>PANEL C - EARLY WARNING SYSTEM (EWS) ALERTS</t>
         </is>
       </c>
-      <c r="C26" s="142" t="n"/>
-      <c r="D26" s="142" t="n"/>
-      <c r="E26" s="142" t="n"/>
-      <c r="F26" s="142" t="n"/>
-      <c r="G26" s="142" t="n"/>
-      <c r="H26" s="142" t="n"/>
-      <c r="I26" s="142" t="n"/>
-      <c r="J26" s="142" t="n"/>
-      <c r="K26" s="142" t="n"/>
-      <c r="L26" s="142" t="n"/>
-      <c r="M26" s="142" t="n"/>
-      <c r="N26" s="142" t="n"/>
-      <c r="O26" s="142" t="n"/>
-      <c r="P26" s="142" t="n"/>
-      <c r="Q26" s="142" t="n"/>
-      <c r="R26" s="142" t="n"/>
-      <c r="S26" s="142" t="n"/>
-      <c r="T26" s="142" t="n"/>
-      <c r="U26" s="142" t="n"/>
-      <c r="V26" s="142" t="n"/>
-      <c r="W26" s="143" t="n"/>
-    </row>
-    <row r="27" ht="25.5" customHeight="1" s="132">
-      <c r="B27" s="152" t="inlineStr">
+      <c r="C26" s="136" t="n"/>
+      <c r="D26" s="136" t="n"/>
+      <c r="E26" s="136" t="n"/>
+      <c r="F26" s="136" t="n"/>
+      <c r="G26" s="136" t="n"/>
+      <c r="H26" s="136" t="n"/>
+      <c r="I26" s="136" t="n"/>
+      <c r="J26" s="136" t="n"/>
+      <c r="K26" s="136" t="n"/>
+      <c r="L26" s="136" t="n"/>
+      <c r="M26" s="136" t="n"/>
+      <c r="N26" s="136" t="n"/>
+      <c r="O26" s="136" t="n"/>
+      <c r="P26" s="136" t="n"/>
+      <c r="Q26" s="136" t="n"/>
+      <c r="R26" s="136" t="n"/>
+      <c r="S26" s="136" t="n"/>
+      <c r="T26" s="136" t="n"/>
+      <c r="U26" s="136" t="n"/>
+      <c r="V26" s="136" t="n"/>
+      <c r="W26" s="137" t="n"/>
+    </row>
+    <row r="27" ht="25.5" customHeight="1" s="140">
+      <c r="B27" s="164" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="C27" s="142" t="n"/>
-      <c r="D27" s="142" t="n"/>
-      <c r="E27" s="142" t="n"/>
-      <c r="F27" s="143" t="n"/>
-      <c r="G27" s="152" t="inlineStr">
+      <c r="C27" s="136" t="n"/>
+      <c r="D27" s="136" t="n"/>
+      <c r="E27" s="136" t="n"/>
+      <c r="F27" s="137" t="n"/>
+      <c r="G27" s="164" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="H27" s="142" t="n"/>
-      <c r="I27" s="142" t="n"/>
-      <c r="J27" s="143" t="n"/>
-      <c r="K27" s="152" t="inlineStr">
+      <c r="H27" s="136" t="n"/>
+      <c r="I27" s="136" t="n"/>
+      <c r="J27" s="137" t="n"/>
+      <c r="K27" s="164" t="inlineStr">
         <is>
           <t>Aktual</t>
         </is>
       </c>
-      <c r="L27" s="143" t="n"/>
+      <c r="L27" s="137" t="n"/>
       <c r="M27" s="12" t="inlineStr">
         <is>
           <t>Aman</t>
@@ -3685,40 +3685,40 @@
           <t>Bahaya</t>
         </is>
       </c>
-      <c r="P27" s="152" t="inlineStr">
+      <c r="P27" s="164" t="inlineStr">
         <is>
           <t>Implikasi Operasional &amp; Finansial</t>
         </is>
       </c>
-      <c r="Q27" s="142" t="n"/>
-      <c r="R27" s="142" t="n"/>
-      <c r="S27" s="142" t="n"/>
-      <c r="T27" s="142" t="n"/>
-      <c r="U27" s="142" t="n"/>
-      <c r="V27" s="142" t="n"/>
-      <c r="W27" s="143" t="n"/>
-    </row>
-    <row r="28" ht="25.5" customHeight="1" s="132">
-      <c r="B28" s="144">
+      <c r="Q27" s="136" t="n"/>
+      <c r="R27" s="136" t="n"/>
+      <c r="S27" s="136" t="n"/>
+      <c r="T27" s="136" t="n"/>
+      <c r="U27" s="136" t="n"/>
+      <c r="V27" s="136" t="n"/>
+      <c r="W27" s="137" t="n"/>
+    </row>
+    <row r="28" ht="25.5" customHeight="1" s="140">
+      <c r="B28" s="178">
         <f>Input_Bulanan!C67</f>
         <v/>
       </c>
-      <c r="C28" s="142" t="n"/>
-      <c r="D28" s="142" t="n"/>
-      <c r="E28" s="142" t="n"/>
-      <c r="F28" s="143" t="n"/>
-      <c r="G28" s="153">
+      <c r="C28" s="136" t="n"/>
+      <c r="D28" s="136" t="n"/>
+      <c r="E28" s="136" t="n"/>
+      <c r="F28" s="137" t="n"/>
+      <c r="G28" s="139">
         <f>Input_Bulanan!D67</f>
         <v/>
       </c>
-      <c r="H28" s="142" t="n"/>
-      <c r="I28" s="142" t="n"/>
-      <c r="J28" s="143" t="n"/>
-      <c r="K28" s="165">
+      <c r="H28" s="136" t="n"/>
+      <c r="I28" s="136" t="n"/>
+      <c r="J28" s="137" t="n"/>
+      <c r="K28" s="176">
         <f>TEXT(Input_Bulanan!E67,"dd-mmm-yy")</f>
         <v/>
       </c>
-      <c r="L28" s="143" t="n"/>
+      <c r="L28" s="137" t="n"/>
       <c r="M28" s="106">
         <f>IF(Input_Bulanan!H67="Aman","V","")</f>
         <v/>
@@ -3731,40 +3731,40 @@
         <f>IF(Input_Bulanan!H67="Bahaya","V","")</f>
         <v/>
       </c>
-      <c r="P28" s="183" t="inlineStr">
+      <c r="P28" s="138" t="inlineStr">
         <is>
           <t>Keterlambatan pengiriman pertama berpotensi memicu klaim dari Offtaker utama.</t>
         </is>
       </c>
-      <c r="Q28" s="142" t="n"/>
-      <c r="R28" s="142" t="n"/>
-      <c r="S28" s="142" t="n"/>
-      <c r="T28" s="142" t="n"/>
-      <c r="U28" s="142" t="n"/>
-      <c r="V28" s="142" t="n"/>
-      <c r="W28" s="143" t="n"/>
-    </row>
-    <row r="29" ht="25.5" customHeight="1" s="132">
-      <c r="B29" s="180">
+      <c r="Q28" s="136" t="n"/>
+      <c r="R28" s="136" t="n"/>
+      <c r="S28" s="136" t="n"/>
+      <c r="T28" s="136" t="n"/>
+      <c r="U28" s="136" t="n"/>
+      <c r="V28" s="136" t="n"/>
+      <c r="W28" s="137" t="n"/>
+    </row>
+    <row r="29" ht="25.5" customHeight="1" s="140">
+      <c r="B29" s="135">
         <f>Input_Bulanan!C68</f>
         <v/>
       </c>
-      <c r="C29" s="142" t="n"/>
-      <c r="D29" s="142" t="n"/>
-      <c r="E29" s="142" t="n"/>
-      <c r="F29" s="143" t="n"/>
-      <c r="G29" s="168">
+      <c r="C29" s="136" t="n"/>
+      <c r="D29" s="136" t="n"/>
+      <c r="E29" s="136" t="n"/>
+      <c r="F29" s="137" t="n"/>
+      <c r="G29" s="171">
         <f>Input_Bulanan!D68</f>
         <v/>
       </c>
-      <c r="H29" s="142" t="n"/>
-      <c r="I29" s="142" t="n"/>
-      <c r="J29" s="143" t="n"/>
-      <c r="K29" s="145">
+      <c r="H29" s="136" t="n"/>
+      <c r="I29" s="136" t="n"/>
+      <c r="J29" s="137" t="n"/>
+      <c r="K29" s="146">
         <f>TEXT(Input_Bulanan!E68,"0%")</f>
         <v/>
       </c>
-      <c r="L29" s="143" t="n"/>
+      <c r="L29" s="137" t="n"/>
       <c r="M29" s="106">
         <f>IF(Input_Bulanan!H68="Aman","V","")</f>
         <v/>
@@ -3777,40 +3777,40 @@
         <f>IF(Input_Bulanan!H68="Bahaya","V","")</f>
         <v/>
       </c>
-      <c r="P29" s="167" t="inlineStr">
+      <c r="P29" s="169" t="inlineStr">
         <is>
           <t>Keterlambatan progres berpotensi menunda tahap commissioning.</t>
         </is>
       </c>
-      <c r="Q29" s="142" t="n"/>
-      <c r="R29" s="142" t="n"/>
-      <c r="S29" s="142" t="n"/>
-      <c r="T29" s="142" t="n"/>
-      <c r="U29" s="142" t="n"/>
-      <c r="V29" s="142" t="n"/>
-      <c r="W29" s="143" t="n"/>
-    </row>
-    <row r="30" ht="25.5" customHeight="1" s="132">
-      <c r="B30" s="144">
+      <c r="Q29" s="136" t="n"/>
+      <c r="R29" s="136" t="n"/>
+      <c r="S29" s="136" t="n"/>
+      <c r="T29" s="136" t="n"/>
+      <c r="U29" s="136" t="n"/>
+      <c r="V29" s="136" t="n"/>
+      <c r="W29" s="137" t="n"/>
+    </row>
+    <row r="30" ht="25.5" customHeight="1" s="140">
+      <c r="B30" s="178">
         <f>Input_Bulanan!C69</f>
         <v/>
       </c>
-      <c r="C30" s="142" t="n"/>
-      <c r="D30" s="142" t="n"/>
-      <c r="E30" s="142" t="n"/>
-      <c r="F30" s="143" t="n"/>
-      <c r="G30" s="153">
+      <c r="C30" s="136" t="n"/>
+      <c r="D30" s="136" t="n"/>
+      <c r="E30" s="136" t="n"/>
+      <c r="F30" s="137" t="n"/>
+      <c r="G30" s="139">
         <f>Input_Bulanan!D69</f>
         <v/>
       </c>
-      <c r="H30" s="142" t="n"/>
-      <c r="I30" s="142" t="n"/>
-      <c r="J30" s="143" t="n"/>
-      <c r="K30" s="166">
+      <c r="H30" s="136" t="n"/>
+      <c r="I30" s="136" t="n"/>
+      <c r="J30" s="137" t="n"/>
+      <c r="K30" s="177">
         <f>TEXT(Input_Bulanan!E69,"0%")</f>
         <v/>
       </c>
-      <c r="L30" s="143" t="n"/>
+      <c r="L30" s="137" t="n"/>
       <c r="M30" s="106">
         <f>IF(Input_Bulanan!H69="Aman","V","")</f>
         <v/>
@@ -3823,174 +3823,174 @@
         <f>IF(Input_Bulanan!H69="Bahaya","V","")</f>
         <v/>
       </c>
-      <c r="P30" s="183" t="inlineStr">
+      <c r="P30" s="138" t="inlineStr">
         <is>
           <t>Belum tercapainya kuota offtake minimal mengancam kelayakan finansial operasi.</t>
         </is>
       </c>
-      <c r="Q30" s="142" t="n"/>
-      <c r="R30" s="142" t="n"/>
-      <c r="S30" s="142" t="n"/>
-      <c r="T30" s="142" t="n"/>
-      <c r="U30" s="142" t="n"/>
-      <c r="V30" s="142" t="n"/>
-      <c r="W30" s="143" t="n"/>
-    </row>
-    <row r="31" ht="25.5" customHeight="1" s="132">
-      <c r="B31" s="180" t="n"/>
-      <c r="C31" s="142" t="n"/>
-      <c r="D31" s="142" t="n"/>
-      <c r="E31" s="142" t="n"/>
-      <c r="F31" s="143" t="n"/>
-      <c r="G31" s="168" t="n"/>
-      <c r="H31" s="142" t="n"/>
-      <c r="I31" s="142" t="n"/>
-      <c r="J31" s="143" t="n"/>
-      <c r="K31" s="145" t="n"/>
-      <c r="L31" s="143" t="n"/>
+      <c r="Q30" s="136" t="n"/>
+      <c r="R30" s="136" t="n"/>
+      <c r="S30" s="136" t="n"/>
+      <c r="T30" s="136" t="n"/>
+      <c r="U30" s="136" t="n"/>
+      <c r="V30" s="136" t="n"/>
+      <c r="W30" s="137" t="n"/>
+    </row>
+    <row r="31" ht="25.5" customHeight="1" s="140">
+      <c r="B31" s="135" t="n"/>
+      <c r="C31" s="136" t="n"/>
+      <c r="D31" s="136" t="n"/>
+      <c r="E31" s="136" t="n"/>
+      <c r="F31" s="137" t="n"/>
+      <c r="G31" s="171" t="n"/>
+      <c r="H31" s="136" t="n"/>
+      <c r="I31" s="136" t="n"/>
+      <c r="J31" s="137" t="n"/>
+      <c r="K31" s="146" t="n"/>
+      <c r="L31" s="137" t="n"/>
       <c r="M31" s="106" t="n"/>
       <c r="N31" s="106" t="n"/>
       <c r="O31" s="106" t="n"/>
-      <c r="P31" s="167" t="n"/>
-      <c r="Q31" s="142" t="n"/>
-      <c r="R31" s="142" t="n"/>
-      <c r="S31" s="142" t="n"/>
-      <c r="T31" s="142" t="n"/>
-      <c r="U31" s="142" t="n"/>
-      <c r="V31" s="142" t="n"/>
-      <c r="W31" s="143" t="n"/>
-    </row>
-    <row r="32" ht="25.5" customHeight="1" s="132">
-      <c r="B32" s="144" t="n"/>
-      <c r="C32" s="142" t="n"/>
-      <c r="D32" s="142" t="n"/>
-      <c r="E32" s="142" t="n"/>
-      <c r="F32" s="143" t="n"/>
-      <c r="G32" s="153" t="n"/>
-      <c r="H32" s="142" t="n"/>
-      <c r="I32" s="142" t="n"/>
-      <c r="J32" s="143" t="n"/>
-      <c r="K32" s="172" t="n"/>
-      <c r="L32" s="143" t="n"/>
+      <c r="P31" s="169" t="n"/>
+      <c r="Q31" s="136" t="n"/>
+      <c r="R31" s="136" t="n"/>
+      <c r="S31" s="136" t="n"/>
+      <c r="T31" s="136" t="n"/>
+      <c r="U31" s="136" t="n"/>
+      <c r="V31" s="136" t="n"/>
+      <c r="W31" s="137" t="n"/>
+    </row>
+    <row r="32" ht="25.5" customHeight="1" s="140">
+      <c r="B32" s="178" t="n"/>
+      <c r="C32" s="136" t="n"/>
+      <c r="D32" s="136" t="n"/>
+      <c r="E32" s="136" t="n"/>
+      <c r="F32" s="137" t="n"/>
+      <c r="G32" s="139" t="n"/>
+      <c r="H32" s="136" t="n"/>
+      <c r="I32" s="136" t="n"/>
+      <c r="J32" s="137" t="n"/>
+      <c r="K32" s="181" t="n"/>
+      <c r="L32" s="137" t="n"/>
       <c r="M32" s="106" t="n"/>
       <c r="N32" s="106" t="n"/>
       <c r="O32" s="106" t="n"/>
-      <c r="P32" s="183" t="n"/>
-      <c r="Q32" s="142" t="n"/>
-      <c r="R32" s="142" t="n"/>
-      <c r="S32" s="142" t="n"/>
-      <c r="T32" s="142" t="n"/>
-      <c r="U32" s="142" t="n"/>
-      <c r="V32" s="142" t="n"/>
-      <c r="W32" s="143" t="n"/>
+      <c r="P32" s="138" t="n"/>
+      <c r="Q32" s="136" t="n"/>
+      <c r="R32" s="136" t="n"/>
+      <c r="S32" s="136" t="n"/>
+      <c r="T32" s="136" t="n"/>
+      <c r="U32" s="136" t="n"/>
+      <c r="V32" s="136" t="n"/>
+      <c r="W32" s="137" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="180" t="n"/>
-      <c r="C33" s="142" t="n"/>
-      <c r="D33" s="142" t="n"/>
-      <c r="E33" s="142" t="n"/>
-      <c r="F33" s="143" t="n"/>
-      <c r="G33" s="168" t="n"/>
-      <c r="H33" s="142" t="n"/>
-      <c r="I33" s="142" t="n"/>
-      <c r="J33" s="143" t="n"/>
-      <c r="K33" s="145" t="n"/>
-      <c r="L33" s="143" t="n"/>
+      <c r="B33" s="135" t="n"/>
+      <c r="C33" s="136" t="n"/>
+      <c r="D33" s="136" t="n"/>
+      <c r="E33" s="136" t="n"/>
+      <c r="F33" s="137" t="n"/>
+      <c r="G33" s="171" t="n"/>
+      <c r="H33" s="136" t="n"/>
+      <c r="I33" s="136" t="n"/>
+      <c r="J33" s="137" t="n"/>
+      <c r="K33" s="146" t="n"/>
+      <c r="L33" s="137" t="n"/>
       <c r="M33" s="106" t="n"/>
       <c r="N33" s="106" t="n"/>
       <c r="O33" s="106" t="n"/>
-      <c r="P33" s="167" t="n"/>
-      <c r="Q33" s="142" t="n"/>
-      <c r="R33" s="142" t="n"/>
-      <c r="S33" s="142" t="n"/>
-      <c r="T33" s="142" t="n"/>
-      <c r="U33" s="142" t="n"/>
-      <c r="V33" s="142" t="n"/>
-      <c r="W33" s="143" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" s="132"/>
-    <row r="35" ht="15" customHeight="1" s="132">
-      <c r="B35" s="173" t="inlineStr">
+      <c r="P33" s="169" t="n"/>
+      <c r="Q33" s="136" t="n"/>
+      <c r="R33" s="136" t="n"/>
+      <c r="S33" s="136" t="n"/>
+      <c r="T33" s="136" t="n"/>
+      <c r="U33" s="136" t="n"/>
+      <c r="V33" s="136" t="n"/>
+      <c r="W33" s="137" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="140"/>
+    <row r="35" ht="15" customHeight="1" s="140">
+      <c r="B35" s="166" t="inlineStr">
         <is>
           <t>PANEL D - EXECUTIVE ACTIONS &amp; DECISION REQUIRED</t>
         </is>
       </c>
-      <c r="C35" s="142" t="n"/>
-      <c r="D35" s="142" t="n"/>
-      <c r="E35" s="142" t="n"/>
-      <c r="F35" s="142" t="n"/>
-      <c r="G35" s="142" t="n"/>
-      <c r="H35" s="142" t="n"/>
-      <c r="I35" s="142" t="n"/>
-      <c r="J35" s="142" t="n"/>
-      <c r="K35" s="142" t="n"/>
-      <c r="L35" s="142" t="n"/>
-      <c r="M35" s="142" t="n"/>
-      <c r="N35" s="142" t="n"/>
-      <c r="O35" s="142" t="n"/>
-      <c r="P35" s="142" t="n"/>
-      <c r="Q35" s="142" t="n"/>
-      <c r="R35" s="142" t="n"/>
-      <c r="S35" s="142" t="n"/>
-      <c r="T35" s="142" t="n"/>
-      <c r="U35" s="142" t="n"/>
-      <c r="V35" s="142" t="n"/>
-      <c r="W35" s="143" t="n"/>
-    </row>
-    <row r="36" ht="33" customHeight="1" s="132">
-      <c r="B36" s="158">
+      <c r="C35" s="136" t="n"/>
+      <c r="D35" s="136" t="n"/>
+      <c r="E35" s="136" t="n"/>
+      <c r="F35" s="136" t="n"/>
+      <c r="G35" s="136" t="n"/>
+      <c r="H35" s="136" t="n"/>
+      <c r="I35" s="136" t="n"/>
+      <c r="J35" s="136" t="n"/>
+      <c r="K35" s="136" t="n"/>
+      <c r="L35" s="136" t="n"/>
+      <c r="M35" s="136" t="n"/>
+      <c r="N35" s="136" t="n"/>
+      <c r="O35" s="136" t="n"/>
+      <c r="P35" s="136" t="n"/>
+      <c r="Q35" s="136" t="n"/>
+      <c r="R35" s="136" t="n"/>
+      <c r="S35" s="136" t="n"/>
+      <c r="T35" s="136" t="n"/>
+      <c r="U35" s="136" t="n"/>
+      <c r="V35" s="136" t="n"/>
+      <c r="W35" s="137" t="n"/>
+    </row>
+    <row r="36" ht="33" customHeight="1" s="140">
+      <c r="B36" s="154">
         <f>"Prioritas 1—2: [1] " &amp; INDEX(Risk_Action_Tracker!E$6:E$15, MATCH(LARGE(Risk_Action_Tracker!Z$6:Z$15, 1), Risk_Action_Tracker!Z$6:Z$15, 0)) &amp; " · [2] " &amp; INDEX(Risk_Action_Tracker!E$6:E$15, MATCH(LARGE(Risk_Action_Tracker!Z$6:Z$15, 2), Risk_Action_Tracker!Z$6:Z$15, 0))</f>
         <v/>
       </c>
-      <c r="C36" s="142" t="n"/>
-      <c r="D36" s="142" t="n"/>
-      <c r="E36" s="142" t="n"/>
-      <c r="F36" s="142" t="n"/>
-      <c r="G36" s="142" t="n"/>
-      <c r="H36" s="142" t="n"/>
-      <c r="I36" s="142" t="n"/>
-      <c r="J36" s="142" t="n"/>
-      <c r="K36" s="142" t="n"/>
-      <c r="L36" s="142" t="n"/>
-      <c r="M36" s="142" t="n"/>
-      <c r="N36" s="142" t="n"/>
-      <c r="O36" s="142" t="n"/>
-      <c r="P36" s="142" t="n"/>
-      <c r="Q36" s="142" t="n"/>
-      <c r="R36" s="142" t="n"/>
-      <c r="S36" s="142" t="n"/>
-      <c r="T36" s="142" t="n"/>
-      <c r="U36" s="142" t="n"/>
-      <c r="V36" s="142" t="n"/>
-      <c r="W36" s="143" t="n"/>
-    </row>
-    <row r="37" ht="42.4" customHeight="1" s="132">
-      <c r="B37" s="158" t="inlineStr">
+      <c r="C36" s="136" t="n"/>
+      <c r="D36" s="136" t="n"/>
+      <c r="E36" s="136" t="n"/>
+      <c r="F36" s="136" t="n"/>
+      <c r="G36" s="136" t="n"/>
+      <c r="H36" s="136" t="n"/>
+      <c r="I36" s="136" t="n"/>
+      <c r="J36" s="136" t="n"/>
+      <c r="K36" s="136" t="n"/>
+      <c r="L36" s="136" t="n"/>
+      <c r="M36" s="136" t="n"/>
+      <c r="N36" s="136" t="n"/>
+      <c r="O36" s="136" t="n"/>
+      <c r="P36" s="136" t="n"/>
+      <c r="Q36" s="136" t="n"/>
+      <c r="R36" s="136" t="n"/>
+      <c r="S36" s="136" t="n"/>
+      <c r="T36" s="136" t="n"/>
+      <c r="U36" s="136" t="n"/>
+      <c r="V36" s="136" t="n"/>
+      <c r="W36" s="137" t="n"/>
+    </row>
+    <row r="37" ht="42.4" customHeight="1" s="140">
+      <c r="B37" s="154" t="inlineStr">
         <is>
           <t>Rincian lengkap: lihat sheet 'Risk_Action_Tracker' - Executive Action Tracker Direksi/PSC.</t>
         </is>
       </c>
-      <c r="C37" s="142" t="n"/>
-      <c r="D37" s="142" t="n"/>
-      <c r="E37" s="142" t="n"/>
-      <c r="F37" s="142" t="n"/>
-      <c r="G37" s="142" t="n"/>
-      <c r="H37" s="142" t="n"/>
-      <c r="I37" s="142" t="n"/>
-      <c r="J37" s="142" t="n"/>
-      <c r="K37" s="142" t="n"/>
-      <c r="L37" s="142" t="n"/>
-      <c r="M37" s="142" t="n"/>
-      <c r="N37" s="142" t="n"/>
-      <c r="O37" s="142" t="n"/>
-      <c r="P37" s="142" t="n"/>
-      <c r="Q37" s="142" t="n"/>
-      <c r="R37" s="142" t="n"/>
-      <c r="S37" s="142" t="n"/>
-      <c r="T37" s="142" t="n"/>
-      <c r="U37" s="142" t="n"/>
-      <c r="V37" s="142" t="n"/>
-      <c r="W37" s="143" t="n"/>
+      <c r="C37" s="136" t="n"/>
+      <c r="D37" s="136" t="n"/>
+      <c r="E37" s="136" t="n"/>
+      <c r="F37" s="136" t="n"/>
+      <c r="G37" s="136" t="n"/>
+      <c r="H37" s="136" t="n"/>
+      <c r="I37" s="136" t="n"/>
+      <c r="J37" s="136" t="n"/>
+      <c r="K37" s="136" t="n"/>
+      <c r="L37" s="136" t="n"/>
+      <c r="M37" s="136" t="n"/>
+      <c r="N37" s="136" t="n"/>
+      <c r="O37" s="136" t="n"/>
+      <c r="P37" s="136" t="n"/>
+      <c r="Q37" s="136" t="n"/>
+      <c r="R37" s="136" t="n"/>
+      <c r="S37" s="136" t="n"/>
+      <c r="T37" s="136" t="n"/>
+      <c r="U37" s="136" t="n"/>
+      <c r="V37" s="136" t="n"/>
+      <c r="W37" s="137" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="98">
@@ -3999,10 +3999,10 @@
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="B10:F11"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G15:I15"/>
     <mergeCell ref="G32:J32"/>
+    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="K8:L9"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="G15:I15"/>
     <mergeCell ref="M21:O21"/>
     <mergeCell ref="G5:L5"/>
     <mergeCell ref="B36:W36"/>
@@ -4032,8 +4032,8 @@
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="P31:W31"/>
     <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="G31:J31"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G31:J31"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="B35:W35"/>
     <mergeCell ref="G6:J7"/>
@@ -4155,70 +4155,70 @@
   <dimension ref="A2:F148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="26" customWidth="1" style="132" min="1" max="1"/>
-    <col width="30" customWidth="1" style="132" min="2" max="2"/>
-    <col width="40" customWidth="1" style="132" min="3" max="3"/>
-    <col width="18.53125" customWidth="1" style="132" min="4" max="4"/>
-    <col width="25" customWidth="1" style="132" min="5" max="6"/>
+    <col width="26" customWidth="1" style="140" min="1" max="1"/>
+    <col width="30" customWidth="1" style="140" min="2" max="2"/>
+    <col width="40" customWidth="1" style="140" min="3" max="3"/>
+    <col width="18.53125" customWidth="1" style="140" min="4" max="4"/>
+    <col width="25" customWidth="1" style="140" min="5" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="132">
-      <c r="A2" s="209" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1" s="140">
+      <c r="A2" s="214" t="inlineStr">
         <is>
           <t>REFERENSI FORMULA &amp; AMBANG BATAS (THRESHOLD) — PROJECT RISK &amp; HEALTH DASHBOARD</t>
         </is>
       </c>
-      <c r="B2" s="209" t="n"/>
-      <c r="C2" s="209" t="n"/>
-      <c r="D2" s="209" t="n"/>
-      <c r="E2" s="209" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="132">
-      <c r="A3" s="133" t="inlineStr">
+      <c r="B2" s="214" t="n"/>
+      <c r="C2" s="214" t="n"/>
+      <c r="D2" s="214" t="n"/>
+      <c r="E2" s="214" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="140">
+      <c r="A3" s="201" t="inlineStr">
         <is>
           <t>Proyek X Project Perusahaan X | Sumber: Standarisasi Eksekutif Project Risk &amp; Health Dashboard (Studi Kelayakan Deloitte; Risk Register Proyek X 2025) &amp; Benchmark PT Pertamina (Persero) - Direktorat Manajemen Risiko / Permen BUMN No.02/2023</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="132">
-      <c r="A5" s="194" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1" s="140">
+      <c r="A5" s="196" t="inlineStr">
         <is>
           <t>1. LIMA PILAR KESEHATAN PROYEK (PROJECT HEALTH) &amp; FORMULA</t>
         </is>
       </c>
-      <c r="B5" s="142" t="n"/>
-      <c r="C5" s="142" t="n"/>
-      <c r="D5" s="142" t="n"/>
-      <c r="E5" s="143" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="132">
-      <c r="A6" s="205" t="inlineStr">
+      <c r="B5" s="136" t="n"/>
+      <c r="C5" s="136" t="n"/>
+      <c r="D5" s="136" t="n"/>
+      <c r="E5" s="137" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="140">
+      <c r="A6" s="198" t="inlineStr">
         <is>
           <t>Pilar</t>
         </is>
       </c>
-      <c r="B6" s="205" t="inlineStr">
+      <c r="B6" s="198" t="inlineStr">
         <is>
           <t>Indikator Utama</t>
         </is>
       </c>
-      <c r="C6" s="205" t="inlineStr">
+      <c r="C6" s="198" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="D6" s="205" t="inlineStr">
+      <c r="D6" s="198" t="inlineStr">
         <is>
           <t>Bobot dalam PHS</t>
         </is>
       </c>
-      <c r="E6" s="205" t="inlineStr">
+      <c r="E6" s="198" t="inlineStr">
         <is>
           <t>Sumber / Referensi</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="45.75" customHeight="1" s="132">
+    <row r="7" ht="45.75" customHeight="1" s="140">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Financial Health</t>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45.75" customHeight="1" s="132">
+    <row r="8" ht="45.75" customHeight="1" s="140">
       <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Schedule Health</t>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45.75" customHeight="1" s="132">
+    <row r="9" ht="45.75" customHeight="1" s="140">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Supply Readiness Index (SRI)</t>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45.75" customHeight="1" s="132">
+    <row r="10" ht="45.75" customHeight="1" s="140">
       <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Project Execution Index (PEI)</t>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45.75" customHeight="1" s="132">
+    <row r="11" ht="45.75" customHeight="1" s="140">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Commercial Readiness Index (CRI)</t>
@@ -4352,58 +4352,58 @@
     <row r="12">
       <c r="D12" s="17" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="132">
+    <row r="13" ht="15" customHeight="1" s="140">
       <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Overall Project Health Score (PHS)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="132">
-      <c r="A14" s="207" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="140">
+      <c r="A14" s="192" t="inlineStr">
         <is>
           <t>PHS = (FinancialScore x 0,20) + (ScheduleScore x 0,20) + (SRI x 0,20) + (PEI x 0,20) + (CRI x 0,20)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="132">
-      <c r="A15" s="192" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="140">
+      <c r="A15" s="210" t="inlineStr">
         <is>
           <t>Catatan: FinancialScore &amp; ScheduleScore dikonversi dari CPI/SPI. Jika indeks &gt;= 1,00, skor = 100 (maksimal). Jika &lt; 1,00, skor = indeks x 100.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="132">
-      <c r="A17" s="194" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="140">
+      <c r="A17" s="196" t="inlineStr">
         <is>
           <t>2. PARAMETER &amp; BOBOT SUPPLY READINESS INDEX (SRI)</t>
         </is>
       </c>
-      <c r="B17" s="142" t="n"/>
-      <c r="C17" s="142" t="n"/>
-      <c r="D17" s="142" t="n"/>
-      <c r="E17" s="143" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="132">
-      <c r="A18" s="205" t="inlineStr">
+      <c r="B17" s="136" t="n"/>
+      <c r="C17" s="136" t="n"/>
+      <c r="D17" s="136" t="n"/>
+      <c r="E17" s="137" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="140">
+      <c r="A18" s="198" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B18" s="205" t="inlineStr">
+      <c r="B18" s="198" t="inlineStr">
         <is>
           <t>Bobot</t>
         </is>
       </c>
-      <c r="C18" s="205" t="inlineStr">
+      <c r="C18" s="198" t="inlineStr">
         <is>
           <t>Deskripsi</t>
         </is>
       </c>
-      <c r="D18" s="142" t="n"/>
-      <c r="E18" s="143" t="n"/>
-    </row>
-    <row r="19" ht="33.75" customHeight="1" s="132">
+      <c r="D18" s="136" t="n"/>
+      <c r="E18" s="137" t="n"/>
+    </row>
+    <row r="19" ht="33.75" customHeight="1" s="140">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Salt Contract</t>
@@ -4412,15 +4412,15 @@
       <c r="B19" s="109" t="n">
         <v>0.25</v>
       </c>
-      <c r="C19" s="190" t="inlineStr">
+      <c r="C19" s="199" t="inlineStr">
         <is>
           <t>Kepastian kontrak pasokan bahan baku garam industri jangka panjang dengan PT Garam maupun pemasok luar negeri.</t>
         </is>
       </c>
-      <c r="D19" s="142" t="n"/>
-      <c r="E19" s="142" t="n"/>
-    </row>
-    <row r="20" ht="33.75" customHeight="1" s="132">
+      <c r="D19" s="136" t="n"/>
+      <c r="E19" s="136" t="n"/>
+    </row>
+    <row r="20" ht="33.75" customHeight="1" s="140">
       <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Salt Inventory</t>
@@ -4434,10 +4434,10 @@
           <t>Kesiapan &amp; kapasitas operasional gudang penyimpanan garam di pelabuhan dan lokasi pabrik.</t>
         </is>
       </c>
-      <c r="D20" s="142" t="n"/>
-      <c r="E20" s="142" t="n"/>
-    </row>
-    <row r="21" ht="33.75" customHeight="1" s="132">
+      <c r="D20" s="136" t="n"/>
+      <c r="E20" s="136" t="n"/>
+    </row>
+    <row r="21" ht="33.75" customHeight="1" s="140">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Supplier Qualification</t>
@@ -4446,15 +4446,15 @@
       <c r="B21" s="109" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="190" t="inlineStr">
+      <c r="C21" s="199" t="inlineStr">
         <is>
           <t>Tingkat pemenuhan kualifikasi teknis dan standar kualitas garam dari para calon pemasok.</t>
         </is>
       </c>
-      <c r="D21" s="142" t="n"/>
-      <c r="E21" s="142" t="n"/>
-    </row>
-    <row r="22" ht="33.75" customHeight="1" s="132">
+      <c r="D21" s="136" t="n"/>
+      <c r="E21" s="136" t="n"/>
+    </row>
+    <row r="22" ht="33.75" customHeight="1" s="140">
       <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Shipping Readiness</t>
@@ -4468,10 +4468,10 @@
           <t>Kesiapan fasilitas pelabuhan, ketersediaan armada kapal logistik, dan jalur bongkar muat garam.</t>
         </is>
       </c>
-      <c r="D22" s="142" t="n"/>
-      <c r="E22" s="142" t="n"/>
-    </row>
-    <row r="23" ht="33.75" customHeight="1" s="132">
+      <c r="D22" s="136" t="n"/>
+      <c r="E22" s="136" t="n"/>
+    </row>
+    <row r="23" ht="33.75" customHeight="1" s="140">
       <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Utility Readiness</t>
@@ -4480,45 +4480,45 @@
       <c r="B23" s="109" t="n">
         <v>0.15</v>
       </c>
-      <c r="C23" s="190" t="inlineStr">
+      <c r="C23" s="199" t="inlineStr">
         <is>
           <t>Jaminan kesiapan tie-in pasokan gas bumi dari SKK Migas, air proses, uap panas, dan ketersediaan daya listrik.</t>
         </is>
       </c>
-      <c r="D23" s="142" t="n"/>
-      <c r="E23" s="142" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="132">
-      <c r="A25" s="194" t="inlineStr">
+      <c r="D23" s="136" t="n"/>
+      <c r="E23" s="136" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="140">
+      <c r="A25" s="196" t="inlineStr">
         <is>
           <t>3. PARAMETER &amp; BOBOT PROJECT EXECUTION INDEX (PEI)</t>
         </is>
       </c>
-      <c r="B25" s="142" t="n"/>
-      <c r="C25" s="142" t="n"/>
-      <c r="D25" s="142" t="n"/>
-      <c r="E25" s="143" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="132">
-      <c r="A26" s="205" t="inlineStr">
+      <c r="B25" s="136" t="n"/>
+      <c r="C25" s="136" t="n"/>
+      <c r="D25" s="136" t="n"/>
+      <c r="E25" s="137" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="140">
+      <c r="A26" s="198" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B26" s="205" t="inlineStr">
+      <c r="B26" s="198" t="inlineStr">
         <is>
           <t>Bobot</t>
         </is>
       </c>
-      <c r="C26" s="205" t="inlineStr">
+      <c r="C26" s="198" t="inlineStr">
         <is>
           <t>Deskripsi</t>
         </is>
       </c>
-      <c r="D26" s="142" t="n"/>
-      <c r="E26" s="143" t="n"/>
-    </row>
-    <row r="27" ht="33.75" customHeight="1" s="132">
+      <c r="D26" s="136" t="n"/>
+      <c r="E26" s="137" t="n"/>
+    </row>
+    <row r="27" ht="33.75" customHeight="1" s="140">
       <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Engineering Progress</t>
@@ -4527,15 +4527,15 @@
       <c r="B27" s="109" t="n">
         <v>0.25</v>
       </c>
-      <c r="C27" s="190" t="inlineStr">
+      <c r="C27" s="199" t="inlineStr">
         <is>
           <t>Persentase penyelesaian gambar kerja detail (DED), dokumen spesifikasi teknis, dan persetujuan vendor drawings.</t>
         </is>
       </c>
-      <c r="D27" s="142" t="n"/>
-      <c r="E27" s="142" t="n"/>
-    </row>
-    <row r="28" ht="33.75" customHeight="1" s="132">
+      <c r="D27" s="136" t="n"/>
+      <c r="E27" s="136" t="n"/>
+    </row>
+    <row r="28" ht="33.75" customHeight="1" s="140">
       <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Procurement Progress</t>
@@ -4549,10 +4549,10 @@
           <t>Kemajuan pengadaan barang, khususnya long lead items (menara karbonasi, kiln dekomposisi, reaktor utama).</t>
         </is>
       </c>
-      <c r="D28" s="142" t="n"/>
-      <c r="E28" s="142" t="n"/>
-    </row>
-    <row r="29" ht="33.75" customHeight="1" s="132">
+      <c r="D28" s="136" t="n"/>
+      <c r="E28" s="136" t="n"/>
+    </row>
+    <row r="29" ht="33.75" customHeight="1" s="140">
       <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Construction Progress</t>
@@ -4561,15 +4561,15 @@
       <c r="B29" s="109" t="n">
         <v>0.35</v>
       </c>
-      <c r="C29" s="190" t="inlineStr">
+      <c r="C29" s="199" t="inlineStr">
         <is>
           <t>Kemajuan fisik konstruksi sipil, pondasi alat berat, struktur baja, instalasi mekanikal, kelistrikan, pemipaan.</t>
         </is>
       </c>
-      <c r="D29" s="142" t="n"/>
-      <c r="E29" s="142" t="n"/>
-    </row>
-    <row r="30" ht="33.75" customHeight="1" s="132">
+      <c r="D29" s="136" t="n"/>
+      <c r="E29" s="136" t="n"/>
+    </row>
+    <row r="30" ht="33.75" customHeight="1" s="140">
       <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Commissioning Preparation</t>
@@ -4583,40 +4583,40 @@
           <t>Penyelesaian dokumen prosedur pengujian, tim start-up, Loop Test instrumen, dan suku cadang awal operasional.</t>
         </is>
       </c>
-      <c r="D30" s="142" t="n"/>
-      <c r="E30" s="142" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" s="132">
-      <c r="A32" s="194" t="inlineStr">
+      <c r="D30" s="136" t="n"/>
+      <c r="E30" s="136" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="140">
+      <c r="A32" s="196" t="inlineStr">
         <is>
           <t>4. PARAMETER &amp; BOBOT COMMERCIAL READINESS INDEX (CRI)</t>
         </is>
       </c>
-      <c r="B32" s="142" t="n"/>
-      <c r="C32" s="142" t="n"/>
-      <c r="D32" s="142" t="n"/>
-      <c r="E32" s="143" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" s="132">
-      <c r="A33" s="205" t="inlineStr">
+      <c r="B32" s="136" t="n"/>
+      <c r="C32" s="136" t="n"/>
+      <c r="D32" s="136" t="n"/>
+      <c r="E32" s="137" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="140">
+      <c r="A33" s="198" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B33" s="205" t="inlineStr">
+      <c r="B33" s="198" t="inlineStr">
         <is>
           <t>Bobot</t>
         </is>
       </c>
-      <c r="C33" s="205" t="inlineStr">
+      <c r="C33" s="198" t="inlineStr">
         <is>
           <t>Deskripsi</t>
         </is>
       </c>
-      <c r="D33" s="142" t="n"/>
-      <c r="E33" s="143" t="n"/>
-    </row>
-    <row r="34" ht="33.75" customHeight="1" s="132">
+      <c r="D33" s="136" t="n"/>
+      <c r="E33" s="137" t="n"/>
+    </row>
+    <row r="34" ht="33.75" customHeight="1" s="140">
       <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Offtake Agreement</t>
@@ -4630,10 +4630,10 @@
           <t>Jumlah volume produk yang telah terikat dalam nota kesepahaman (MOU/Offtake Agreement) dengan pembeli domestik.</t>
         </is>
       </c>
-      <c r="D34" s="142" t="n"/>
-      <c r="E34" s="142" t="n"/>
-    </row>
-    <row r="35" ht="33.75" customHeight="1" s="132">
+      <c r="D34" s="136" t="n"/>
+      <c r="E34" s="136" t="n"/>
+    </row>
+    <row r="35" ht="33.75" customHeight="1" s="140">
       <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Marketing Strategy</t>
@@ -4642,15 +4642,15 @@
       <c r="B35" s="109" t="n">
         <v>0.2</v>
       </c>
-      <c r="C35" s="190" t="inlineStr">
+      <c r="C35" s="199" t="inlineStr">
         <is>
           <t>Kesiapan strategi penetapan harga kompetitif terhadap produk impor dan diversifikasi varian produk.</t>
         </is>
       </c>
-      <c r="D35" s="142" t="n"/>
-      <c r="E35" s="142" t="n"/>
-    </row>
-    <row r="36" ht="33.75" customHeight="1" s="132">
+      <c r="D35" s="136" t="n"/>
+      <c r="E35" s="136" t="n"/>
+    </row>
+    <row r="36" ht="33.75" customHeight="1" s="140">
       <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Distribution Readiness</t>
@@ -4664,10 +4664,10 @@
           <t>Kesiapan logistik pengiriman produk akhir: bagging unit, armada pengangkutan darat, konveyor pelabuhan.</t>
         </is>
       </c>
-      <c r="D36" s="142" t="n"/>
-      <c r="E36" s="142" t="n"/>
-    </row>
-    <row r="37" ht="33.75" customHeight="1" s="132">
+      <c r="D36" s="136" t="n"/>
+      <c r="E36" s="136" t="n"/>
+    </row>
+    <row r="37" ht="33.75" customHeight="1" s="140">
       <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Operation Team Ready</t>
@@ -4676,15 +4676,15 @@
       <c r="B37" s="109" t="n">
         <v>0.2</v>
       </c>
-      <c r="C37" s="190" t="inlineStr">
+      <c r="C37" s="199" t="inlineStr">
         <is>
           <t>Kesiapan tim operasi pabrik: sertifikasi operator, SOP pengoperasian, pelatihan simulasi kondisi darurat.</t>
         </is>
       </c>
-      <c r="D37" s="142" t="n"/>
-      <c r="E37" s="142" t="n"/>
-    </row>
-    <row r="38" ht="33.75" customHeight="1" s="132">
+      <c r="D37" s="136" t="n"/>
+      <c r="E37" s="136" t="n"/>
+    </row>
+    <row r="38" ht="33.75" customHeight="1" s="140">
       <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Product Qualification</t>
@@ -4698,53 +4698,53 @@
           <t>Kesiapan laboratorium pengujian mutu produk &amp; sertifikasi SNI agar memenuhi kualifikasi industri premium.</t>
         </is>
       </c>
-      <c r="D38" s="142" t="n"/>
-      <c r="E38" s="142" t="n"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" s="132">
-      <c r="A40" s="194" t="inlineStr">
+      <c r="D38" s="136" t="n"/>
+      <c r="E38" s="136" t="n"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="140">
+      <c r="A40" s="196" t="inlineStr">
         <is>
           <t>5. TABEL BATAS TOLERANSI (THRESHOLD) - SISTEM RAG (RED-AMBER-GREEN)</t>
         </is>
       </c>
-      <c r="B40" s="142" t="n"/>
-      <c r="C40" s="142" t="n"/>
-      <c r="D40" s="142" t="n"/>
-      <c r="E40" s="143" t="n"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" s="132">
-      <c r="A41" s="195" t="inlineStr">
+      <c r="B40" s="136" t="n"/>
+      <c r="C40" s="136" t="n"/>
+      <c r="D40" s="136" t="n"/>
+      <c r="E40" s="137" t="n"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="140">
+      <c r="A41" s="194" t="inlineStr">
         <is>
           <t>Pilar Kesehatan</t>
         </is>
       </c>
-      <c r="B41" s="195" t="inlineStr">
+      <c r="B41" s="194" t="inlineStr">
         <is>
           <t>Indikator</t>
         </is>
       </c>
-      <c r="C41" s="195" t="inlineStr">
+      <c r="C41" s="194" t="inlineStr">
         <is>
           <t>Hijau</t>
         </is>
       </c>
-      <c r="D41" s="195" t="inlineStr">
+      <c r="D41" s="194" t="inlineStr">
         <is>
           <t>Kuning</t>
         </is>
       </c>
-      <c r="E41" s="195" t="inlineStr">
+      <c r="E41" s="194" t="inlineStr">
         <is>
           <t>Oranye</t>
         </is>
       </c>
-      <c r="F41" s="195" t="inlineStr">
+      <c r="F41" s="194" t="inlineStr">
         <is>
           <t>Merah</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="132">
+    <row r="42" ht="15.75" customHeight="1" s="140">
       <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Financial Health</t>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="132">
+    <row r="43" ht="15.75" customHeight="1" s="140">
       <c r="A43" s="28" t="inlineStr">
         <is>
           <t>Schedule Health</t>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="132">
+    <row r="44" ht="15.75" customHeight="1" s="140">
       <c r="A44" s="23" t="inlineStr">
         <is>
           <t>Supply Readiness</t>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="132">
+    <row r="45" ht="15.75" customHeight="1" s="140">
       <c r="A45" s="28" t="inlineStr">
         <is>
           <t>Project Execution</t>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="132">
+    <row r="46" ht="15.75" customHeight="1" s="140">
       <c r="A46" s="23" t="inlineStr">
         <is>
           <t>Commercial Readiness</t>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="132">
+    <row r="47" ht="15.75" customHeight="1" s="140">
       <c r="A47" s="28" t="inlineStr">
         <is>
           <t>Overall Health</t>
@@ -4936,44 +4936,44 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="132">
-      <c r="A49" s="194" t="inlineStr">
+    <row r="49" ht="15.75" customHeight="1" s="140">
+      <c r="A49" s="196" t="inlineStr">
         <is>
           <t>6. KRITERIA LIKELIHOOD (PROBABILITAS) - MATRIKS RISIKO 5x5</t>
         </is>
       </c>
-      <c r="B49" s="142" t="n"/>
-      <c r="C49" s="142" t="n"/>
-      <c r="D49" s="142" t="n"/>
-      <c r="E49" s="143" t="n"/>
-    </row>
-    <row r="50" ht="21.75" customHeight="1" s="132">
-      <c r="A50" s="204" t="inlineStr">
+      <c r="B49" s="136" t="n"/>
+      <c r="C49" s="136" t="n"/>
+      <c r="D49" s="136" t="n"/>
+      <c r="E49" s="137" t="n"/>
+    </row>
+    <row r="50" ht="21.75" customHeight="1" s="140">
+      <c r="A50" s="205" t="inlineStr">
         <is>
           <t>Catatan: kriteria berikut merupakan kriteria standar manajemen risiko (ISO 31000 &amp; benchmark Pertamina RCSA/KRI). Sesuaikan dengan Pedoman Manajemen Risiko Perusahaan X resmi apabila tersedia angka baku internal.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1" s="132">
-      <c r="A51" s="195" t="inlineStr">
+    <row r="51" ht="15.75" customHeight="1" s="140">
+      <c r="A51" s="194" t="inlineStr">
         <is>
           <t>Level (L)</t>
         </is>
       </c>
-      <c r="B51" s="195" t="inlineStr">
+      <c r="B51" s="194" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C51" s="195" t="inlineStr">
+      <c r="C51" s="194" t="inlineStr">
         <is>
           <t>Kriteria Probabilitas Kejadian</t>
         </is>
       </c>
-      <c r="D51" s="142" t="n"/>
-      <c r="E51" s="143" t="n"/>
-    </row>
-    <row r="52" ht="25.5" customHeight="1" s="132">
+      <c r="D51" s="136" t="n"/>
+      <c r="E51" s="137" t="n"/>
+    </row>
+    <row r="52" ht="25.5" customHeight="1" s="140">
       <c r="A52" s="29" t="n">
         <v>1</v>
       </c>
@@ -4982,15 +4982,15 @@
           <t>Sangat Jarang Terjadi</t>
         </is>
       </c>
-      <c r="C52" s="189" t="inlineStr">
+      <c r="C52" s="197" t="inlineStr">
         <is>
           <t>Kemungkinan terjadi &lt; 10% selama siklus proyek; belum pernah terjadi pada proyek sejenis.</t>
         </is>
       </c>
-      <c r="D52" s="142" t="n"/>
-      <c r="E52" s="142" t="n"/>
-    </row>
-    <row r="53" ht="25.5" customHeight="1" s="132">
+      <c r="D52" s="136" t="n"/>
+      <c r="E52" s="136" t="n"/>
+    </row>
+    <row r="53" ht="25.5" customHeight="1" s="140">
       <c r="A53" s="31" t="n">
         <v>2</v>
       </c>
@@ -4999,15 +4999,15 @@
           <t>Jarang Terjadi</t>
         </is>
       </c>
-      <c r="C53" s="191" t="inlineStr">
+      <c r="C53" s="195" t="inlineStr">
         <is>
           <t>Kemungkinan terjadi 10-30%; pernah terjadi namun jarang pada proyek EPC sejenis.</t>
         </is>
       </c>
-      <c r="D53" s="142" t="n"/>
-      <c r="E53" s="142" t="n"/>
-    </row>
-    <row r="54" ht="25.5" customHeight="1" s="132">
+      <c r="D53" s="136" t="n"/>
+      <c r="E53" s="136" t="n"/>
+    </row>
+    <row r="54" ht="25.5" customHeight="1" s="140">
       <c r="A54" s="33" t="n">
         <v>3</v>
       </c>
@@ -5016,15 +5016,15 @@
           <t>Bisa Terjadi</t>
         </is>
       </c>
-      <c r="C54" s="189" t="inlineStr">
+      <c r="C54" s="197" t="inlineStr">
         <is>
           <t>Kemungkinan terjadi 30-50%; pernah terjadi beberapa kali pada proyek sejenis.</t>
         </is>
       </c>
-      <c r="D54" s="142" t="n"/>
-      <c r="E54" s="142" t="n"/>
-    </row>
-    <row r="55" ht="25.5" customHeight="1" s="132">
+      <c r="D54" s="136" t="n"/>
+      <c r="E54" s="136" t="n"/>
+    </row>
+    <row r="55" ht="25.5" customHeight="1" s="140">
       <c r="A55" s="34" t="n">
         <v>4</v>
       </c>
@@ -5033,15 +5033,15 @@
           <t>Sangat Mungkin Terjadi</t>
         </is>
       </c>
-      <c r="C55" s="191" t="inlineStr">
+      <c r="C55" s="195" t="inlineStr">
         <is>
           <t>Kemungkinan terjadi 50-70%; kondisi/indikasi saat ini mengarah pada terjadinya risiko.</t>
         </is>
       </c>
-      <c r="D55" s="142" t="n"/>
-      <c r="E55" s="142" t="n"/>
-    </row>
-    <row r="56" ht="25.5" customHeight="1" s="132">
+      <c r="D55" s="136" t="n"/>
+      <c r="E55" s="136" t="n"/>
+    </row>
+    <row r="56" ht="25.5" customHeight="1" s="140">
       <c r="A56" s="35" t="n">
         <v>5</v>
       </c>
@@ -5050,45 +5050,45 @@
           <t>Hampir Pasti Terjadi</t>
         </is>
       </c>
-      <c r="C56" s="189" t="inlineStr">
+      <c r="C56" s="197" t="inlineStr">
         <is>
           <t>Kemungkinan terjadi &gt; 70%; sudah terdapat indikasi kuat / sedang berlangsung saat ini.</t>
         </is>
       </c>
-      <c r="D56" s="142" t="n"/>
-      <c r="E56" s="142" t="n"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" s="132">
-      <c r="A58" s="194" t="inlineStr">
+      <c r="D56" s="136" t="n"/>
+      <c r="E56" s="136" t="n"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" s="140">
+      <c r="A58" s="196" t="inlineStr">
         <is>
           <t>7. KRITERIA CONSEQUENCE (DAMPAK) - MATRIKS RISIKO 5x5</t>
         </is>
       </c>
-      <c r="B58" s="142" t="n"/>
-      <c r="C58" s="142" t="n"/>
-      <c r="D58" s="142" t="n"/>
-      <c r="E58" s="143" t="n"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" s="132">
-      <c r="A59" s="195" t="inlineStr">
+      <c r="B58" s="136" t="n"/>
+      <c r="C58" s="136" t="n"/>
+      <c r="D58" s="136" t="n"/>
+      <c r="E58" s="137" t="n"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" s="140">
+      <c r="A59" s="194" t="inlineStr">
         <is>
           <t>Level (C)</t>
         </is>
       </c>
-      <c r="B59" s="195" t="inlineStr">
+      <c r="B59" s="194" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C59" s="195" t="inlineStr">
+      <c r="C59" s="194" t="inlineStr">
         <is>
           <t>Kriteria Dampak (Finansial / Jadwal / Reputasi)</t>
         </is>
       </c>
-      <c r="D59" s="142" t="n"/>
-      <c r="E59" s="143" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1" s="132">
+      <c r="D59" s="136" t="n"/>
+      <c r="E59" s="137" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1" s="140">
       <c r="A60" s="29" t="n">
         <v>1</v>
       </c>
@@ -5097,15 +5097,15 @@
           <t>Sangat Rendah</t>
         </is>
       </c>
-      <c r="C60" s="189" t="inlineStr">
+      <c r="C60" s="197" t="inlineStr">
         <is>
           <t>Dampak biaya &lt; USD 0,5 Juta; keterlambatan jadwal &lt; 1 minggu; tanpa dampak reputasi/K3.</t>
         </is>
       </c>
-      <c r="D60" s="142" t="n"/>
-      <c r="E60" s="142" t="n"/>
-    </row>
-    <row r="61" ht="30" customHeight="1" s="132">
+      <c r="D60" s="136" t="n"/>
+      <c r="E60" s="136" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1" s="140">
       <c r="A61" s="31" t="n">
         <v>2</v>
       </c>
@@ -5114,15 +5114,15 @@
           <t>Rendah</t>
         </is>
       </c>
-      <c r="C61" s="191" t="inlineStr">
+      <c r="C61" s="195" t="inlineStr">
         <is>
           <t>Dampak biaya USD 0,5-2 Juta; keterlambatan jadwal 1-4 minggu; keluhan internal, dapat dikelola PIC.</t>
         </is>
       </c>
-      <c r="D61" s="142" t="n"/>
-      <c r="E61" s="142" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1" s="132">
+      <c r="D61" s="136" t="n"/>
+      <c r="E61" s="136" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1" s="140">
       <c r="A62" s="33" t="n">
         <v>3</v>
       </c>
@@ -5131,15 +5131,15 @@
           <t>Moderat</t>
         </is>
       </c>
-      <c r="C62" s="189" t="inlineStr">
+      <c r="C62" s="197" t="inlineStr">
         <is>
           <t>Dampak biaya USD 2-10 Juta; keterlambatan jadwal 1-2 bulan; perhatian manajemen menengah/PSC.</t>
         </is>
       </c>
-      <c r="D62" s="142" t="n"/>
-      <c r="E62" s="142" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1" s="132">
+      <c r="D62" s="136" t="n"/>
+      <c r="E62" s="136" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1" s="140">
       <c r="A63" s="34" t="n">
         <v>4</v>
       </c>
@@ -5148,15 +5148,15 @@
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="C63" s="191" t="inlineStr">
+      <c r="C63" s="195" t="inlineStr">
         <is>
           <t>Dampak biaya USD 10-30 Juta; keterlambatan jadwal 2-6 bulan; berisiko pada target COD &amp; perhatian Direksi.</t>
         </is>
       </c>
-      <c r="D63" s="142" t="n"/>
-      <c r="E63" s="142" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1" s="132">
+      <c r="D63" s="136" t="n"/>
+      <c r="E63" s="136" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1" s="140">
       <c r="A64" s="35" t="n">
         <v>5</v>
       </c>
@@ -5165,52 +5165,52 @@
           <t>Sangat Tinggi</t>
         </is>
       </c>
-      <c r="C64" s="189" t="inlineStr">
+      <c r="C64" s="197" t="inlineStr">
         <is>
           <t>Dampak biaya &gt; USD 30 Juta; keterlambatan &gt; 6 bulan atau mengancam kegagalan COD; berdampak pada kelayakan NPV proyek &amp; reputasi korporat.</t>
         </is>
       </c>
-      <c r="D64" s="142" t="n"/>
-      <c r="E64" s="142" t="n"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" s="132">
-      <c r="A66" s="194" t="inlineStr">
+      <c r="D64" s="136" t="n"/>
+      <c r="E64" s="136" t="n"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="140">
+      <c r="A66" s="196" t="inlineStr">
         <is>
           <t>8. KLASIFIKASI LEVEL RISIKO - 5 TINGKAT (Pedoman Manajemen Risiko Perusahaan X)</t>
         </is>
       </c>
-      <c r="B66" s="142" t="n"/>
-      <c r="C66" s="142" t="n"/>
-      <c r="D66" s="142" t="n"/>
-      <c r="E66" s="143" t="n"/>
-    </row>
-    <row r="67" ht="19.5" customHeight="1" s="132">
+      <c r="B66" s="136" t="n"/>
+      <c r="C66" s="136" t="n"/>
+      <c r="D66" s="136" t="n"/>
+      <c r="E66" s="137" t="n"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1" s="140">
       <c r="A67" s="206" t="inlineStr">
         <is>
           <t>Skor Matriks L x C TIDAK lagi dihitung dari perkalian langsung L x C dengan pembagian rentang rata, melainkan menggunakan Tabel Skala Risiko Non-Linear (Skala 1-25) pada bagian 10 di bawah, yang memprioritaskan bobot Consequence (Dampak) dibanding Likelihood (Probabilitas) untuk kombinasi bernilai sama — konsisten dengan pendekatan penentuan level risiko non-linear yang lazim digunakan pada matriks 5x5 ISO 31000:2018 / AS-NZS ISO 31000 dan praktik matriks risiko K3/SMKP BUMN sektor energi-tambang (rujukan pola: Kepdirjen Minerba No.1827.K/30/MEM/2018). Overall Risk Index (skala 0-100, benchmark Pertamina) tetap memakai rentang rata seperti semula.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1" s="132">
-      <c r="A68" s="195" t="inlineStr">
+    <row r="68" ht="15.75" customHeight="1" s="140">
+      <c r="A68" s="194" t="inlineStr">
         <is>
           <t>Level Risiko</t>
         </is>
       </c>
-      <c r="B68" s="195" t="inlineStr">
+      <c r="B68" s="194" t="inlineStr">
         <is>
           <t>Skor Matriks L x C (1-25)</t>
         </is>
       </c>
-      <c r="C68" s="195" t="inlineStr">
+      <c r="C68" s="194" t="inlineStr">
         <is>
           <t>Overall Risk Index (0-100)</t>
         </is>
       </c>
-      <c r="D68" s="142" t="n"/>
-      <c r="E68" s="143" t="n"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" s="132">
+      <c r="D68" s="136" t="n"/>
+      <c r="E68" s="137" t="n"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" s="140">
       <c r="A69" s="36" t="inlineStr">
         <is>
           <t>Low</t>
@@ -5221,15 +5221,15 @@
           <t>1 - 5</t>
         </is>
       </c>
-      <c r="C69" s="198" t="inlineStr">
+      <c r="C69" s="200" t="inlineStr">
         <is>
           <t>0 - 20</t>
         </is>
       </c>
-      <c r="D69" s="142" t="n"/>
-      <c r="E69" s="142" t="n"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" s="132">
+      <c r="D69" s="136" t="n"/>
+      <c r="E69" s="136" t="n"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" s="140">
       <c r="A70" s="38" t="inlineStr">
         <is>
           <t>Low to Moderate</t>
@@ -5240,15 +5240,15 @@
           <t>6 - 11</t>
         </is>
       </c>
-      <c r="C70" s="198" t="inlineStr">
+      <c r="C70" s="200" t="inlineStr">
         <is>
           <t>21 - 40</t>
         </is>
       </c>
-      <c r="D70" s="142" t="n"/>
-      <c r="E70" s="142" t="n"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" s="132">
+      <c r="D70" s="136" t="n"/>
+      <c r="E70" s="136" t="n"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" s="140">
       <c r="A71" s="39" t="inlineStr">
         <is>
           <t>Moderate</t>
@@ -5259,15 +5259,15 @@
           <t>12 - 15</t>
         </is>
       </c>
-      <c r="C71" s="198" t="inlineStr">
+      <c r="C71" s="200" t="inlineStr">
         <is>
           <t>41 - 60</t>
         </is>
       </c>
-      <c r="D71" s="142" t="n"/>
-      <c r="E71" s="142" t="n"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" s="132">
+      <c r="D71" s="136" t="n"/>
+      <c r="E71" s="136" t="n"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" s="140">
       <c r="A72" s="40" t="inlineStr">
         <is>
           <t>Moderate to High</t>
@@ -5278,15 +5278,15 @@
           <t>16 - 19</t>
         </is>
       </c>
-      <c r="C72" s="198" t="inlineStr">
+      <c r="C72" s="200" t="inlineStr">
         <is>
           <t>61 - 80</t>
         </is>
       </c>
-      <c r="D72" s="142" t="n"/>
-      <c r="E72" s="142" t="n"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" s="132">
+      <c r="D72" s="136" t="n"/>
+      <c r="E72" s="136" t="n"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="140">
       <c r="A73" s="41" t="inlineStr">
         <is>
           <t>High</t>
@@ -5297,26 +5297,26 @@
           <t>20 - 25</t>
         </is>
       </c>
-      <c r="C73" s="198" t="inlineStr">
+      <c r="C73" s="200" t="inlineStr">
         <is>
           <t>81 - 100</t>
         </is>
       </c>
-      <c r="D73" s="142" t="n"/>
-      <c r="E73" s="142" t="n"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" s="132">
-      <c r="A75" s="194" t="inlineStr">
+      <c r="D73" s="136" t="n"/>
+      <c r="E73" s="136" t="n"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="140">
+      <c r="A75" s="196" t="inlineStr">
         <is>
           <t>9. KOMPOSISI SUB-INDEKS OVERALL RISK INDEX (BENCHMARK PERTAMINA)</t>
         </is>
       </c>
-      <c r="B75" s="142" t="n"/>
-      <c r="C75" s="142" t="n"/>
-      <c r="D75" s="142" t="n"/>
-      <c r="E75" s="143" t="n"/>
-    </row>
-    <row r="76" ht="30" customHeight="1" s="132">
+      <c r="B75" s="136" t="n"/>
+      <c r="C75" s="136" t="n"/>
+      <c r="D75" s="136" t="n"/>
+      <c r="E75" s="137" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1" s="140">
       <c r="A76" s="19" t="inlineStr">
         <is>
           <t>Supply Risk Index</t>
@@ -5325,15 +5325,15 @@
       <c r="B76" s="110" t="n">
         <v>0.4</v>
       </c>
-      <c r="C76" s="189" t="inlineStr">
+      <c r="C76" s="197" t="inlineStr">
         <is>
           <t>Bahan baku garam industri, kualitas garam lokal vs impor, keandalan pemasok, risiko logistik maritim, kesiapan gudang, kesiapan utilitas.</t>
         </is>
       </c>
-      <c r="D76" s="142" t="n"/>
-      <c r="E76" s="142" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1" s="132">
+      <c r="D76" s="136" t="n"/>
+      <c r="E76" s="136" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1" s="140">
       <c r="A77" s="15" t="inlineStr">
         <is>
           <t>Execution Risk Index</t>
@@ -5342,15 +5342,15 @@
       <c r="B77" s="109" t="n">
         <v>0.4</v>
       </c>
-      <c r="C77" s="191" t="inlineStr">
+      <c r="C77" s="195" t="inlineStr">
         <is>
           <t>Kesiapan rekayasa desain, pengadaan peralatan utama, produktivitas tenaga kerja, antarmuka antar-EPC, pengapalan long lead items, kesiapan uji fungsi.</t>
         </is>
       </c>
-      <c r="D77" s="142" t="n"/>
-      <c r="E77" s="142" t="n"/>
-    </row>
-    <row r="78" ht="30" customHeight="1" s="132">
+      <c r="D77" s="136" t="n"/>
+      <c r="E77" s="136" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1" s="140">
       <c r="A78" s="19" t="inlineStr">
         <is>
           <t>Commercial Risk Index</t>
@@ -5359,32 +5359,32 @@
       <c r="B78" s="110" t="n">
         <v>0.2</v>
       </c>
-      <c r="C78" s="189" t="inlineStr">
+      <c r="C78" s="197" t="inlineStr">
         <is>
           <t>Pengikatan kontrak offtake, fluktuasi harga Proyek X global, tekanan produk impor, kesiapan logistik distribusi hilir, sertifikasi kualitas produk.</t>
         </is>
       </c>
-      <c r="D78" s="142" t="n"/>
-      <c r="E78" s="142" t="n"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" s="132">
-      <c r="A79" s="196" t="inlineStr">
+      <c r="D78" s="136" t="n"/>
+      <c r="E78" s="136" t="n"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="140">
+      <c r="A79" s="211" t="inlineStr">
         <is>
           <t>Overall Risk Index = (Supply Risk Index x 0,40) + (Execution Risk Index x 0,40) + (Commercial Risk Index x 0,20)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="132">
+    <row r="81" ht="15" customHeight="1" s="140">
       <c r="A81" s="42" t="inlineStr">
         <is>
           <t>Sumber benchmark tata kelola risiko: PT Pertamina (Persero) - Direktorat Manajemen Risiko (2nd Line of Defense, Permen BUMN No.02/2023), Komite Tata Kelola Terintegrasi (KTKT), Gate Review/FID, RCSA, KRI, ICT, C-RBDD; PT Biro Klasifikasi Indonesia (Persero) - SK-6/2023 (Risk Appetite berbasis Net Working Capital); klasifikasi 5-tingkat Low/Low to Moderate/Moderate/Moderate to High/High mengikuti nomenklatur Pedoman Manajemen Risiko Perusahaan X.</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="132"/>
-    <row r="83" ht="15" customHeight="1" s="132"/>
-    <row r="84" ht="15" customHeight="1" s="132"/>
-    <row r="86" ht="14.25" customHeight="1" s="132">
+    <row r="82" ht="15" customHeight="1" s="140"/>
+    <row r="83" ht="15" customHeight="1" s="140"/>
+    <row r="84" ht="15" customHeight="1" s="140"/>
+    <row r="86" ht="14.25" customHeight="1" s="140">
       <c r="A86" s="43" t="inlineStr">
         <is>
           <t>10. TABEL SKALA RISIKO (RISK RANKING) 5x5 NON-LINEAR &amp; WARNA HEAT MAP</t>
@@ -5396,14 +5396,14 @@
       <c r="E86" s="44" t="n"/>
       <c r="F86" s="44" t="n"/>
     </row>
-    <row r="87" ht="43.5" customHeight="1" s="132">
-      <c r="A87" s="199" t="inlineStr">
+    <row r="87" ht="43.5" customHeight="1" s="140">
+      <c r="A87" s="207" t="inlineStr">
         <is>
           <t>Tabel skala risiko berikut menetapkan urutan (rank) 1-25 untuk setiap 25 kombinasi Likelihood (L) x Consequence (C) sesuai spesifikasi metodologi risiko internal yang ditetapkan Project Control Proyek X Perusahaan X. Berbeda dari perkalian L x C sederhana, urutan ini memberi bobot lebih besar pada Consequence saat terjadi nilai sama, mengikuti kaidah umum non-linear risk ranking pada standar ISO 31000:2018 dan praktik matriks risiko korporasi BUMN. Skala menentukan posisi &amp; warna sel pada Risk Profile Heat Map di sheet Dashboard.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="14.25" customHeight="1" s="132">
+    <row r="89" ht="14.25" customHeight="1" s="140">
       <c r="A89" s="12" t="inlineStr">
         <is>
           <t>Key (L x10 + C)</t>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="14.25" customHeight="1" s="132">
+    <row r="90" ht="14.25" customHeight="1" s="140">
       <c r="A90" s="45" t="n">
         <v>11</v>
       </c>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="14.25" customHeight="1" s="132">
+    <row r="91" ht="14.25" customHeight="1" s="140">
       <c r="A91" s="45" t="n">
         <v>21</v>
       </c>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="14.25" customHeight="1" s="132">
+    <row r="92" ht="14.25" customHeight="1" s="140">
       <c r="A92" s="45" t="n">
         <v>31</v>
       </c>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="14.25" customHeight="1" s="132">
+    <row r="93" ht="14.25" customHeight="1" s="140">
       <c r="A93" s="45" t="n">
         <v>41</v>
       </c>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="14.25" customHeight="1" s="132">
+    <row r="94" ht="14.25" customHeight="1" s="140">
       <c r="A94" s="45" t="n">
         <v>12</v>
       </c>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="14.25" customHeight="1" s="132">
+    <row r="95" ht="14.25" customHeight="1" s="140">
       <c r="A95" s="45" t="n">
         <v>22</v>
       </c>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="14.25" customHeight="1" s="132">
+    <row r="96" ht="14.25" customHeight="1" s="140">
       <c r="A96" s="45" t="n">
         <v>51</v>
       </c>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="14.25" customHeight="1" s="132">
+    <row r="97" ht="14.25" customHeight="1" s="140">
       <c r="A97" s="45" t="n">
         <v>32</v>
       </c>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="14.25" customHeight="1" s="132">
+    <row r="98" ht="14.25" customHeight="1" s="140">
       <c r="A98" s="45" t="n">
         <v>42</v>
       </c>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="14.25" customHeight="1" s="132">
+    <row r="99" ht="14.25" customHeight="1" s="140">
       <c r="A99" s="45" t="n">
         <v>13</v>
       </c>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="14.25" customHeight="1" s="132">
+    <row r="100" ht="14.25" customHeight="1" s="140">
       <c r="A100" s="45" t="n">
         <v>23</v>
       </c>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="14.25" customHeight="1" s="132">
+    <row r="101" ht="14.25" customHeight="1" s="140">
       <c r="A101" s="45" t="n">
         <v>52</v>
       </c>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="14.25" customHeight="1" s="132">
+    <row r="102" ht="14.25" customHeight="1" s="140">
       <c r="A102" s="45" t="n">
         <v>33</v>
       </c>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="14.25" customHeight="1" s="132">
+    <row r="103" ht="14.25" customHeight="1" s="140">
       <c r="A103" s="45" t="n">
         <v>43</v>
       </c>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="14.25" customHeight="1" s="132">
+    <row r="104" ht="14.25" customHeight="1" s="140">
       <c r="A104" s="45" t="n">
         <v>14</v>
       </c>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="14.25" customHeight="1" s="132">
+    <row r="105" ht="14.25" customHeight="1" s="140">
       <c r="A105" s="45" t="n">
         <v>24</v>
       </c>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="14.25" customHeight="1" s="132">
+    <row r="106" ht="14.25" customHeight="1" s="140">
       <c r="A106" s="45" t="n">
         <v>53</v>
       </c>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="14.25" customHeight="1" s="132">
+    <row r="107" ht="14.25" customHeight="1" s="140">
       <c r="A107" s="45" t="n">
         <v>34</v>
       </c>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="14.25" customHeight="1" s="132">
+    <row r="108" ht="14.25" customHeight="1" s="140">
       <c r="A108" s="45" t="n">
         <v>44</v>
       </c>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="14.25" customHeight="1" s="132">
+    <row r="109" ht="14.25" customHeight="1" s="140">
       <c r="A109" s="45" t="n">
         <v>15</v>
       </c>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="14.25" customHeight="1" s="132">
+    <row r="110" ht="14.25" customHeight="1" s="140">
       <c r="A110" s="45" t="n">
         <v>25</v>
       </c>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="14.25" customHeight="1" s="132">
+    <row r="111" ht="14.25" customHeight="1" s="140">
       <c r="A111" s="45" t="n">
         <v>54</v>
       </c>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="14.25" customHeight="1" s="132">
+    <row r="112" ht="14.25" customHeight="1" s="140">
       <c r="A112" s="45" t="n">
         <v>35</v>
       </c>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="14.25" customHeight="1" s="132">
+    <row r="113" ht="14.25" customHeight="1" s="140">
       <c r="A113" s="45" t="n">
         <v>45</v>
       </c>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="14.25" customHeight="1" s="132">
+    <row r="114" ht="14.25" customHeight="1" s="140">
       <c r="A114" s="45" t="n">
         <v>55</v>
       </c>
@@ -6035,14 +6035,14 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="31.5" customHeight="1" s="132">
-      <c r="A116" s="199" t="inlineStr">
+    <row r="116" ht="31.5" customHeight="1" s="140">
+      <c r="A116" s="207" t="inlineStr">
         <is>
           <t>Sumber/Referensi Tabel Skala: metodologi non-linear risk ranking ISO 31000:2018 (klausul 5.4.3 - penentuan level risiko); praktik matriks 5x5 K3/SMKP BUMN sektor energi &amp; tambang; disesuaikan dengan nomenklatur 5-tingkat Pedoman Manajemen Risiko Perusahaan X (Low / Low to Moderate / Moderate / Moderate to High / High).</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="14.25" customHeight="1" s="132">
+    <row r="118" ht="14.25" customHeight="1" s="140">
       <c r="A118" s="43" t="inlineStr">
         <is>
           <t>11. METODOLOGI EARLY WARNING SYSTEM (EWS) — 3 STATUS (AMAN / WASPADA / BAHAYA)</t>
@@ -6054,76 +6054,76 @@
       <c r="E118" s="44" t="n"/>
       <c r="F118" s="44" t="n"/>
     </row>
-    <row r="119" ht="33.75" customHeight="1" s="132">
-      <c r="A119" s="199" t="inlineStr">
+    <row r="119" ht="33.75" customHeight="1" s="140">
+      <c r="A119" s="207" t="inlineStr">
         <is>
           <t>Setiap parameter EWS diklasifikasikan ke 3 status menggunakan pendekatan Key Risk Indicator (KRI) Traffic Light dengan buffer toleransi 10% dari threshold sebagai batas Waspada (Amber Zone), mengacu pada COSO Enterprise Risk Management Framework (2017) dan praktik RCSA-KRI PT Pertamina (Persero) yang telah dirujuk pada dokumen ini.</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="14.25" customHeight="1" s="132">
-      <c r="A121" s="208" t="inlineStr">
+    <row r="121" ht="14.25" customHeight="1" s="140">
+      <c r="A121" s="209" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B121" s="208" t="inlineStr">
+      <c r="B121" s="209" t="inlineStr">
         <is>
           <t>Definisi Ambang Batas (untuk indikator "semakin tinggi semakin baik")</t>
         </is>
       </c>
-      <c r="E121" s="208" t="inlineStr">
+      <c r="E121" s="209" t="inlineStr">
         <is>
           <t>Warna</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="14.25" customHeight="1" s="132">
+    <row r="122" ht="14.25" customHeight="1" s="140">
       <c r="A122" s="52" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="B122" s="201" t="inlineStr">
+      <c r="B122" s="202" t="inlineStr">
         <is>
           <t>Nilai Aktual &gt;= Threshold (100% dari batas aman)</t>
         </is>
       </c>
-      <c r="C122" s="202" t="n"/>
-      <c r="D122" s="203" t="n"/>
+      <c r="C122" s="203" t="n"/>
+      <c r="D122" s="204" t="n"/>
       <c r="E122" s="53" t="n"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1" s="132">
+    <row r="123" ht="14.25" customHeight="1" s="140">
       <c r="A123" s="54" t="inlineStr">
         <is>
           <t>Waspada</t>
         </is>
       </c>
-      <c r="B123" s="201" t="inlineStr">
+      <c r="B123" s="202" t="inlineStr">
         <is>
           <t>Threshold x 90% &lt;= Nilai Aktual &lt; Threshold</t>
         </is>
       </c>
-      <c r="C123" s="202" t="n"/>
-      <c r="D123" s="203" t="n"/>
+      <c r="C123" s="203" t="n"/>
+      <c r="D123" s="204" t="n"/>
       <c r="E123" s="53" t="n"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1" s="132">
+    <row r="124" ht="14.25" customHeight="1" s="140">
       <c r="A124" s="55" t="inlineStr">
         <is>
           <t>Bahaya</t>
         </is>
       </c>
-      <c r="B124" s="201" t="inlineStr">
+      <c r="B124" s="202" t="inlineStr">
         <is>
           <t>Nilai Aktual &lt; Threshold x 90%</t>
         </is>
       </c>
-      <c r="C124" s="202" t="n"/>
-      <c r="D124" s="203" t="n"/>
+      <c r="C124" s="203" t="n"/>
+      <c r="D124" s="204" t="n"/>
       <c r="E124" s="53" t="n"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1" s="132">
+    <row r="127" ht="15.75" customHeight="1" s="140">
       <c r="A127" s="92" t="inlineStr">
         <is>
           <t>12. METODOLOGI PERHITUNGAN SUB-INDEKS RISIKO</t>
@@ -6136,7 +6136,7 @@
       <c r="F127" s="93" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="197" t="inlineStr">
+      <c r="A129" s="212" t="inlineStr">
         <is>
           <t>Masing-masing sub-indeks risiko dihitung melalui metode penilaian pakar (expert scoring) pada skala 0-100:</t>
         </is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="57" customHeight="1" s="132">
+    <row r="131" ht="57" customHeight="1" s="140">
       <c r="A131" s="95" t="inlineStr">
         <is>
           <t>Supply Risk Index</t>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="57" customHeight="1" s="132">
+    <row r="132" ht="57" customHeight="1" s="140">
       <c r="A132" s="95" t="inlineStr">
         <is>
           <t>Execution Risk Index</t>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="28.5" customHeight="1" s="132">
+    <row r="133" ht="28.5" customHeight="1" s="140">
       <c r="A133" s="95" t="inlineStr">
         <is>
           <t>Commercial Risk Index</t>
@@ -6271,7 +6271,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="138" t="inlineStr">
+      <c r="A136" s="189" t="inlineStr">
         <is>
           <t>Formula Overall Risk Index = (Supply Risk Index × 0,4) + (Execution Risk Index × 0,4) + (Commercial Risk Index × 0,2)</t>
         </is>
@@ -6290,7 +6290,7 @@
       <c r="F139" s="93" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="200" t="inlineStr">
+      <c r="A141" s="208" t="inlineStr">
         <is>
           <t>Setiap risiko dalam register diklasifikasi berdasarkan Skala Risiko Non-Linear 5x5 (bagian 10) ke dalam 5 tingkat risiko Perusahaan X:</t>
         </is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="15.75" customHeight="1" s="132">
+    <row r="147" ht="15.75" customHeight="1" s="140">
       <c r="A147" s="100" t="inlineStr">
         <is>
           <t>Low to Moderate</t>
@@ -6420,9 +6420,9 @@
     <mergeCell ref="C71:E71"/>
     <mergeCell ref="C52:E52"/>
     <mergeCell ref="A116:F116"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C23:E23"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="C70:E70"/>
     <mergeCell ref="A75:E75"/>
@@ -6442,7 +6442,6 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="C78:E78"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A67:E67"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C68:E68"/>
@@ -6453,16 +6452,17 @@
     <mergeCell ref="B121:D121"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="B122:D122"/>
+    <mergeCell ref="C63:E63"/>
     <mergeCell ref="C73:E73"/>
     <mergeCell ref="A119:F119"/>
+    <mergeCell ref="C26:E26"/>
     <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C26:E26"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A87:F87"/>
-    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -6479,26 +6479,26 @@
   <dimension ref="C2:I78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="2" customWidth="1" style="132" min="1" max="1"/>
-    <col width="3" customWidth="1" style="132" min="2" max="2"/>
-    <col width="58.796875" customWidth="1" style="132" min="3" max="3"/>
-    <col width="25.33203125" bestFit="1" customWidth="1" style="132" min="4" max="4"/>
-    <col width="27.19921875" bestFit="1" customWidth="1" style="132" min="5" max="5"/>
-    <col width="20.59765625" bestFit="1" customWidth="1" style="132" min="6" max="6"/>
-    <col width="38" customWidth="1" style="132" min="7" max="7"/>
-    <col width="16.73046875" bestFit="1" customWidth="1" style="132" min="8" max="8"/>
-    <col width="20" customWidth="1" style="132" min="9" max="9"/>
+    <col width="2" customWidth="1" style="140" min="1" max="1"/>
+    <col width="3" customWidth="1" style="140" min="2" max="2"/>
+    <col width="58.796875" customWidth="1" style="140" min="3" max="3"/>
+    <col width="25.33203125" bestFit="1" customWidth="1" style="140" min="4" max="4"/>
+    <col width="27.19921875" bestFit="1" customWidth="1" style="140" min="5" max="5"/>
+    <col width="20.59765625" bestFit="1" customWidth="1" style="140" min="6" max="6"/>
+    <col width="38" customWidth="1" style="140" min="7" max="7"/>
+    <col width="16.73046875" bestFit="1" customWidth="1" style="140" min="8" max="8"/>
+    <col width="20" customWidth="1" style="140" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="132">
-      <c r="C2" s="209" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1" s="140">
+      <c r="C2" s="214" t="inlineStr">
         <is>
           <t>INPUT DATA BULANAN — DIISI OLEH PIC / PROJECT CONTROL SETIAP PERIODE PELAPORAN</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="132">
-      <c r="C3" s="133" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="140">
+      <c r="C3" s="201" t="inlineStr">
         <is>
           <t>Sel KUNING (font biru) = input manual. Sel ABU-ABU = formula otomatis, jangan diubah manual. Arahkan kursor ke label bertanda (i) untuk penjelasan parameter.</t>
         </is>
@@ -6510,7 +6510,7 @@
           <t>Nama Perusahaan</t>
         </is>
       </c>
-      <c r="D4" s="125">
+      <c r="D4" s="124">
         <f>Config!B6</f>
         <v/>
       </c>
@@ -6519,21 +6519,19 @@
           <t>Nama Proyek</t>
         </is>
       </c>
-      <c r="G4" s="125">
+      <c r="G4" s="124">
         <f>Config!B7</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="132">
+    <row r="5" ht="15.75" customHeight="1" s="140">
       <c r="C5" s="56" t="inlineStr">
         <is>
           <t>Periode Pelaporan (Bulan/Tahun)</t>
         </is>
       </c>
-      <c r="D5" s="57" t="inlineStr">
-        <is>
-          <t>Agustus 2026</t>
-        </is>
+      <c r="D5" s="134" t="n">
+        <v>46266</v>
       </c>
       <c r="E5" s="56" t="inlineStr">
         <is>
@@ -6542,25 +6540,25 @@
       </c>
       <c r="F5" s="57" t="inlineStr">
         <is>
-          <t>DRAFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19.5" customHeight="1" s="132">
-      <c r="C7" s="131" t="inlineStr">
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" s="140">
+      <c r="C7" s="213" t="inlineStr">
         <is>
           <t>1. EARNED VALUE MANAGEMENT (EVM) — FINANCIAL &amp; SCHEDULE HEALTH  (satuan: USD Juta, kumulatif)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="132">
+    <row r="8" ht="15.75" customHeight="1" s="140">
       <c r="C8" s="58" t="inlineStr">
         <is>
           <t>Planned Value (PV) — kumulatif s.d. periode ini</t>
         </is>
       </c>
       <c r="D8" s="59" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -6568,7 +6566,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="132">
+    <row r="9" ht="15.75" customHeight="1" s="140">
       <c r="C9" s="58" t="inlineStr">
         <is>
           <t>Earned Value (EV) — kumulatif s.d. periode ini</t>
@@ -6578,7 +6576,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="132">
+    <row r="10" ht="15.75" customHeight="1" s="140">
       <c r="C10" s="58" t="inlineStr">
         <is>
           <t>Actual Cost (AC) — kumulatif s.d. periode ini</t>
@@ -6588,7 +6586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="132">
+    <row r="11" ht="15.75" customHeight="1" s="140">
       <c r="C11" s="58" t="inlineStr">
         <is>
           <t>Net Present Value (NPV) — USD Juta</t>
@@ -6598,7 +6596,7 @@
         <v>77.59999999999999</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="132">
+    <row r="12" ht="15.75" customHeight="1" s="140">
       <c r="C12" s="56" t="inlineStr">
         <is>
           <t>Cost Performance Index (CPI = EV/AC)</t>
@@ -6609,7 +6607,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="132">
+    <row r="13" ht="15.75" customHeight="1" s="140">
       <c r="C13" s="56" t="inlineStr">
         <is>
           <t>Cost Variance (CV = EV-AC), USD Juta</t>
@@ -6620,7 +6618,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="132">
+    <row r="14" ht="15.75" customHeight="1" s="140">
       <c r="C14" s="56" t="inlineStr">
         <is>
           <t>Schedule Performance Index (SPI = EV/PV)</t>
@@ -6631,7 +6629,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="132">
+    <row r="15" ht="15.75" customHeight="1" s="140">
       <c r="C15" s="56" t="inlineStr">
         <is>
           <t>Schedule Variance (SV = EV-PV), USD Juta</t>
@@ -6642,14 +6640,14 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1" s="132">
-      <c r="C17" s="131" t="inlineStr">
+    <row r="17" ht="19.5" customHeight="1" s="140">
+      <c r="C17" s="213" t="inlineStr">
         <is>
           <t>2. SUPPLY READINESS INDEX (SRI) — skor kesiapan tiap parameter</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="132">
+    <row r="18" ht="15.75" customHeight="1" s="140">
       <c r="C18" s="58" t="inlineStr">
         <is>
           <t>Salt Contract</t>
@@ -6658,16 +6656,16 @@
       <c r="D18" s="62" t="n">
         <v>0.82</v>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="125">
         <f>Referensi_Threshold!B19</f>
         <v/>
       </c>
-      <c r="F18" s="127">
+      <c r="F18" s="126">
         <f>D18*E18</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="132">
+    <row r="19" ht="15.75" customHeight="1" s="140">
       <c r="C19" s="58" t="inlineStr">
         <is>
           <t>Salt Inventory</t>
@@ -6676,16 +6674,16 @@
       <c r="D19" s="62" t="n">
         <v>0.8</v>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="125">
         <f>Referensi_Threshold!B20</f>
         <v/>
       </c>
-      <c r="F19" s="127">
+      <c r="F19" s="126">
         <f>D19*E19</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="132">
+    <row r="20" ht="15.75" customHeight="1" s="140">
       <c r="C20" s="58" t="inlineStr">
         <is>
           <t>Supplier Qualification</t>
@@ -6694,16 +6692,16 @@
       <c r="D20" s="62" t="n">
         <v>0.75</v>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="125">
         <f>Referensi_Threshold!B21</f>
         <v/>
       </c>
-      <c r="F20" s="127">
+      <c r="F20" s="126">
         <f>D20*E20</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="132">
+    <row r="21" ht="15.75" customHeight="1" s="140">
       <c r="C21" s="58" t="inlineStr">
         <is>
           <t>Shipping Readiness</t>
@@ -6712,16 +6710,16 @@
       <c r="D21" s="62" t="n">
         <v>0.85</v>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="125">
         <f>Referensi_Threshold!B22</f>
         <v/>
       </c>
-      <c r="F21" s="127">
+      <c r="F21" s="126">
         <f>D21*E21</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="132">
+    <row r="22" ht="15.75" customHeight="1" s="140">
       <c r="C22" s="58" t="inlineStr">
         <is>
           <t>Utility Readiness</t>
@@ -6730,16 +6728,16 @@
       <c r="D22" s="62" t="n">
         <v>0.8</v>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="125">
         <f>Referensi_Threshold!B23</f>
         <v/>
       </c>
-      <c r="F22" s="127">
+      <c r="F22" s="126">
         <f>D22*E22</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="132">
+    <row r="23" ht="15.75" customHeight="1" s="140">
       <c r="C23" s="58" t="inlineStr">
         <is>
           <t>Salt Readiness</t>
@@ -6748,42 +6746,42 @@
       <c r="D23" s="62" t="n">
         <v>0.8</v>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="125">
         <f>Referensi_Threshold!B24</f>
         <v/>
       </c>
-      <c r="F23" s="127">
+      <c r="F23" s="126">
         <f>D23*E23</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="132">
+    <row r="24" ht="15.75" customHeight="1" s="140">
       <c r="C24" s="56" t="inlineStr">
         <is>
           <t>SRI — Supply Readiness Index (tertimbang)</t>
         </is>
       </c>
-      <c r="D24" s="128">
+      <c r="D24" s="127">
         <f>F24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="125">
         <f>SUM(E18:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="129">
+      <c r="F24" s="128">
         <f>SUM(F18:F23)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="132">
-      <c r="C26" s="131" t="inlineStr">
+    <row r="26" ht="19.5" customHeight="1" s="140">
+      <c r="C26" s="213" t="inlineStr">
         <is>
           <t>3. PROJECT EXECUTION INDEX (PEI) — progres aktual tiap parameter</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="132">
+    <row r="27" ht="15.75" customHeight="1" s="140">
       <c r="C27" s="58" t="inlineStr">
         <is>
           <t>Engineering Progress</t>
@@ -6792,16 +6790,16 @@
       <c r="D27" s="62" t="n">
         <v>0.88</v>
       </c>
-      <c r="E27" s="126">
+      <c r="E27" s="125">
         <f>Referensi_Threshold!B27</f>
         <v/>
       </c>
-      <c r="F27" s="127">
+      <c r="F27" s="126">
         <f>D27*E27</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="132">
+    <row r="28" ht="15.75" customHeight="1" s="140">
       <c r="C28" s="58" t="inlineStr">
         <is>
           <t>Procurement Progress</t>
@@ -6810,16 +6808,16 @@
       <c r="D28" s="62" t="n">
         <v>0.73</v>
       </c>
-      <c r="E28" s="126">
+      <c r="E28" s="125">
         <f>Referensi_Threshold!B28</f>
         <v/>
       </c>
-      <c r="F28" s="127">
+      <c r="F28" s="126">
         <f>D28*E28</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="132">
+    <row r="29" ht="15.75" customHeight="1" s="140">
       <c r="C29" s="58" t="inlineStr">
         <is>
           <t>Construction Progress</t>
@@ -6828,16 +6826,16 @@
       <c r="D29" s="62" t="n">
         <v>0.82</v>
       </c>
-      <c r="E29" s="126">
+      <c r="E29" s="125">
         <f>Referensi_Threshold!B29</f>
         <v/>
       </c>
-      <c r="F29" s="127">
+      <c r="F29" s="126">
         <f>D29*E29</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="132">
+    <row r="30" ht="15.75" customHeight="1" s="140">
       <c r="C30" s="58" t="inlineStr">
         <is>
           <t>Commissioning Preparation</t>
@@ -6846,16 +6844,16 @@
       <c r="D30" s="62" t="n">
         <v>0.42</v>
       </c>
-      <c r="E30" s="126">
+      <c r="E30" s="125">
         <f>Referensi_Threshold!B30</f>
         <v/>
       </c>
-      <c r="F30" s="127">
+      <c r="F30" s="126">
         <f>D30*E30</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="132">
+    <row r="31" ht="15.75" customHeight="1" s="140">
       <c r="C31" s="58" t="inlineStr">
         <is>
           <t>Pencapaian Performance Test</t>
@@ -6864,35 +6862,35 @@
       <c r="D31" s="62" t="n">
         <v>0.4</v>
       </c>
-      <c r="E31" s="126">
+      <c r="E31" s="125">
         <f>Referensi_Threshold!B31</f>
         <v/>
       </c>
-      <c r="F31" s="127">
+      <c r="F31" s="126">
         <f>D31*E31</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="132">
+    <row r="32" ht="15.75" customHeight="1" s="140">
       <c r="C32" s="56" t="inlineStr">
         <is>
           <t>PEI — Project Execution Index (tertimbang)</t>
         </is>
       </c>
-      <c r="D32" s="128">
+      <c r="D32" s="127">
         <f>F32</f>
         <v/>
       </c>
-      <c r="E32" s="126">
+      <c r="E32" s="125">
         <f>SUM(E27:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="129">
+      <c r="F32" s="128">
         <f>SUM(F27:F31)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="132">
+    <row r="33" ht="15.75" customHeight="1" s="140">
       <c r="C33" s="58" t="inlineStr">
         <is>
           <t>Deviasi Kemajuan Fisik vs Target (S-Curve)</t>
@@ -6902,14 +6900,14 @@
         <v>0.058</v>
       </c>
     </row>
-    <row r="35" ht="19.5" customHeight="1" s="132">
-      <c r="C35" s="131" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1" s="140">
+      <c r="C35" s="213" t="inlineStr">
         <is>
           <t>4. COMMERCIAL READINESS INDEX (CRI) — skor kesiapan tiap parameter</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="132">
+    <row r="36" ht="15.75" customHeight="1" s="140">
       <c r="C36" s="58" t="inlineStr">
         <is>
           <t>Offtake Agreement</t>
@@ -6918,16 +6916,16 @@
       <c r="D36" s="62" t="n">
         <v>0.6</v>
       </c>
-      <c r="E36" s="126">
+      <c r="E36" s="125">
         <f>Referensi_Threshold!B34</f>
         <v/>
       </c>
-      <c r="F36" s="127">
+      <c r="F36" s="126">
         <f>D36*E36</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="132">
+    <row r="37" ht="15.75" customHeight="1" s="140">
       <c r="C37" s="58" t="inlineStr">
         <is>
           <t>Marketing Strategy</t>
@@ -6936,16 +6934,16 @@
       <c r="D37" s="62" t="n">
         <v>0.6</v>
       </c>
-      <c r="E37" s="126">
+      <c r="E37" s="125">
         <f>Referensi_Threshold!B35</f>
         <v/>
       </c>
-      <c r="F37" s="127">
+      <c r="F37" s="126">
         <f>D37*E37</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="132">
+    <row r="38" ht="15.75" customHeight="1" s="140">
       <c r="C38" s="58" t="inlineStr">
         <is>
           <t>Distribution Readiness</t>
@@ -6954,16 +6952,16 @@
       <c r="D38" s="62" t="n">
         <v>0.8</v>
       </c>
-      <c r="E38" s="126">
+      <c r="E38" s="125">
         <f>Referensi_Threshold!B36</f>
         <v/>
       </c>
-      <c r="F38" s="127">
+      <c r="F38" s="126">
         <f>D38*E38</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="132">
+    <row r="39" ht="15.75" customHeight="1" s="140">
       <c r="C39" s="58" t="inlineStr">
         <is>
           <t>Operation Team Ready</t>
@@ -6972,16 +6970,16 @@
       <c r="D39" s="62" t="n">
         <v>0.8</v>
       </c>
-      <c r="E39" s="126">
+      <c r="E39" s="125">
         <f>Referensi_Threshold!B37</f>
         <v/>
       </c>
-      <c r="F39" s="127">
+      <c r="F39" s="126">
         <f>D39*E39</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="132">
+    <row r="40" ht="15.75" customHeight="1" s="140">
       <c r="C40" s="58" t="inlineStr">
         <is>
           <t>Product Qualification</t>
@@ -6990,16 +6988,16 @@
       <c r="D40" s="62" t="n">
         <v>0.4</v>
       </c>
-      <c r="E40" s="126">
+      <c r="E40" s="125">
         <f>Referensi_Threshold!B38</f>
         <v/>
       </c>
-      <c r="F40" s="127">
+      <c r="F40" s="126">
         <f>D40*E40</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="132">
+    <row r="41" ht="15.75" customHeight="1" s="140">
       <c r="C41" s="58" t="inlineStr">
         <is>
           <t>Regulatory Readiness</t>
@@ -7008,42 +7006,42 @@
       <c r="D41" s="62" t="n">
         <v>0.5</v>
       </c>
-      <c r="E41" s="126">
+      <c r="E41" s="125">
         <f>Referensi_Threshold!B39</f>
         <v/>
       </c>
-      <c r="F41" s="127">
+      <c r="F41" s="126">
         <f>D41*E41</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="132">
+    <row r="42" ht="15.75" customHeight="1" s="140">
       <c r="C42" s="56" t="inlineStr">
         <is>
           <t>CRI — Commercial Readiness Index (tertimbang)</t>
         </is>
       </c>
-      <c r="D42" s="128">
+      <c r="D42" s="127">
         <f>F42</f>
         <v/>
       </c>
-      <c r="E42" s="126">
+      <c r="E42" s="125">
         <f>SUM(E36:E41)</f>
         <v/>
       </c>
-      <c r="F42" s="129">
+      <c r="F42" s="128">
         <f>SUM(F36:F41)</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="19.5" customHeight="1" s="132">
-      <c r="C44" s="131" t="inlineStr">
+    <row r="44" ht="19.5" customHeight="1" s="140">
+      <c r="C44" s="213" t="inlineStr">
         <is>
           <t>5. OVERALL RISK INDEX — sub-indeks risiko (skor 0-100, benchmark Pertamina)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="132">
+    <row r="45" ht="15.75" customHeight="1" s="140">
       <c r="C45" s="58" t="inlineStr">
         <is>
           <t>Supply Risk Index (bobot 40%)</t>
@@ -7053,12 +7051,12 @@
         <f>D24*100</f>
         <v/>
       </c>
-      <c r="E45" s="130">
+      <c r="E45" s="129">
         <f>Config!B21</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="132">
+    <row r="46" ht="15.75" customHeight="1" s="140">
       <c r="C46" s="58" t="inlineStr">
         <is>
           <t>Execution Risk Index (bobot 40%)</t>
@@ -7068,12 +7066,12 @@
         <f>D32*100</f>
         <v/>
       </c>
-      <c r="E46" s="130">
+      <c r="E46" s="129">
         <f>Config!B22</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="132">
+    <row r="47" ht="15.75" customHeight="1" s="140">
       <c r="C47" s="58" t="inlineStr">
         <is>
           <t>Commercial Risk Index (bobot 20%)</t>
@@ -7083,12 +7081,12 @@
         <f>D42*100</f>
         <v/>
       </c>
-      <c r="E47" s="130">
+      <c r="E47" s="129">
         <f>Config!B23</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="132">
+    <row r="48" ht="15.75" customHeight="1" s="140">
       <c r="C48" s="56" t="inlineStr">
         <is>
           <t>Overall Risk Index (tertimbang, skala 0-100)</t>
@@ -7099,7 +7097,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="132">
+    <row r="49" ht="15.75" customHeight="1" s="140">
       <c r="C49" s="56" t="inlineStr">
         <is>
           <t>Overall Risk Level (5 Tingkat, formula)</t>
@@ -7110,14 +7108,14 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="19.5" customHeight="1" s="132">
-      <c r="C51" s="131" t="inlineStr">
+    <row r="51" ht="19.5" customHeight="1" s="140">
+      <c r="C51" s="213" t="inlineStr">
         <is>
           <t>6. REGISTER RISIKO AKTIF — Jumlah Risiko per 5 Tingkat Perusahaan X</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="132">
+    <row r="52" ht="15.75" customHeight="1" s="140">
       <c r="C52" s="86" t="inlineStr">
         <is>
           <t>High</t>
@@ -7127,7 +7125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="132">
+    <row r="53" ht="15.75" customHeight="1" s="140">
       <c r="C53" s="87" t="inlineStr">
         <is>
           <t>Moderate to High</t>
@@ -7137,7 +7135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1" s="132">
+    <row r="54" ht="15.75" customHeight="1" s="140">
       <c r="C54" s="88" t="inlineStr">
         <is>
           <t>Moderate</t>
@@ -7147,7 +7145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="132">
+    <row r="55" ht="15.75" customHeight="1" s="140">
       <c r="C55" s="89" t="inlineStr">
         <is>
           <t>Low to Moderate</t>
@@ -7157,7 +7155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="132">
+    <row r="56" ht="15.75" customHeight="1" s="140">
       <c r="C56" s="85" t="inlineStr">
         <is>
           <t>Low</t>
@@ -7178,15 +7176,15 @@
         <v/>
       </c>
     </row>
-    <row r="58" ht="19.5" customHeight="1" s="132"/>
-    <row r="59" ht="15.75" customHeight="1" s="132">
-      <c r="C59" s="131" t="inlineStr">
+    <row r="58" ht="19.5" customHeight="1" s="140"/>
+    <row r="59" ht="15.75" customHeight="1" s="140">
+      <c r="C59" s="213" t="inlineStr">
         <is>
           <t>7. STATUS MITIGASI &amp; DINAMIKA PERGERAKAN RISIKO (BULAN BERJALAN)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="132">
+    <row r="60" ht="15.75" customHeight="1" s="140">
       <c r="C60" s="58" t="inlineStr">
         <is>
           <t>Completed Mitigations (%)</t>
@@ -7204,7 +7202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="132">
+    <row r="61" ht="15.75" customHeight="1" s="140">
       <c r="C61" s="58" t="inlineStr">
         <is>
           <t>Overdue Actions (%)</t>
@@ -7222,7 +7220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="132">
+    <row r="62" ht="15.75" customHeight="1" s="140">
       <c r="C62" s="58" t="inlineStr">
         <is>
           <t>On Track Mitigations (%)</t>
@@ -7240,7 +7238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" ht="38.25" customHeight="1" s="132">
+    <row r="63" ht="38.25" customHeight="1" s="140">
       <c r="C63" s="58" t="inlineStr">
         <is>
           <t>Need Escalation (jumlah aksi)</t>
@@ -7258,26 +7256,26 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" ht="19.5" customHeight="1" s="132"/>
-    <row r="65" ht="15.75" customHeight="1" s="132">
-      <c r="C65" s="131" t="inlineStr">
+    <row r="64" ht="19.5" customHeight="1" s="140"/>
+    <row r="65" ht="15.75" customHeight="1" s="140">
+      <c r="C65" s="213" t="inlineStr">
         <is>
           <t>8. EARLY WARNING SYSTEM (EWS) — NILAI AKTUAL PEMANTAUAN</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1" s="132">
-      <c r="C66" s="205" t="inlineStr">
+    <row r="66" ht="15.75" customHeight="1" s="140">
+      <c r="C66" s="198" t="inlineStr">
         <is>
           <t>Parameter EWS</t>
         </is>
       </c>
-      <c r="D66" s="205" t="inlineStr">
+      <c r="D66" s="198" t="inlineStr">
         <is>
           <t>Threshold (Batas Aman)</t>
         </is>
       </c>
-      <c r="E66" s="205" t="inlineStr">
+      <c r="E66" s="198" t="inlineStr">
         <is>
           <t>Nilai Aktual</t>
         </is>
@@ -7298,21 +7296,21 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1" s="132">
+    <row r="67" ht="15.75" customHeight="1" s="140">
       <c r="C67" s="58" t="inlineStr">
         <is>
           <t>First Shipment</t>
         </is>
       </c>
-      <c r="D67" s="216" t="inlineStr">
+      <c r="D67" s="132" t="inlineStr">
         <is>
           <t>Target (Threshold)</t>
         </is>
       </c>
-      <c r="E67" s="217" t="n">
+      <c r="E67" s="133" t="n">
         <v>46113</v>
       </c>
-      <c r="F67" s="114" t="n">
+      <c r="F67" s="113" t="n">
         <v>46096</v>
       </c>
       <c r="G67" s="68" t="inlineStr">
@@ -7325,7 +7323,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1" s="132">
+    <row r="68" ht="15.75" customHeight="1" s="140">
       <c r="C68" s="58" t="inlineStr">
         <is>
           <t>Project Progress</t>
@@ -7352,7 +7350,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" ht="15.75" customHeight="1" s="132">
+    <row r="69" ht="15.75" customHeight="1" s="140">
       <c r="C69" s="58" t="inlineStr">
         <is>
           <t>Offtaker Agreement</t>
@@ -7379,66 +7377,65 @@
         <v/>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71" ht="19.5" customHeight="1" s="132"/>
-    <row r="72" ht="15.75" customHeight="1" s="132">
-      <c r="C72" s="131" t="inlineStr">
+    <row r="71" ht="19.5" customHeight="1" s="140"/>
+    <row r="72" ht="15.75" customHeight="1" s="140">
+      <c r="C72" s="213" t="inlineStr">
         <is>
           <t>9. TOP RISK REGISTER (C1-C4) — INPUT LIKELIHOOD (L) &amp; CONSEQUENCE (C) UNTUK HEAT MAP</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1" s="132">
-      <c r="C73" s="192" t="inlineStr">
+    <row r="73" ht="15.75" customHeight="1" s="140">
+      <c r="C73" s="210" t="inlineStr">
         <is>
           <t>Skala Risiko &amp; Risk Level dihitung otomatis dari Tabel Skala Risiko Non-Linear 5x5 pada sheet Referensi_Threshold bagian 10 (bukan lagi perkalian L x C sederhana). Posisi pada Risk Profile Heat Map di sheet Dashboard mengikuti nilai L &amp; C ini secara otomatis.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="27.75" customHeight="1" s="132">
-      <c r="C74" s="195" t="inlineStr">
+    <row r="74" ht="27.75" customHeight="1" s="140">
+      <c r="C74" s="194" t="inlineStr">
         <is>
           <t>Kode</t>
         </is>
       </c>
-      <c r="D74" s="195" t="inlineStr">
+      <c r="D74" s="194" t="inlineStr">
         <is>
           <t>Deskripsi Risiko Utama</t>
         </is>
       </c>
-      <c r="E74" s="195" t="inlineStr">
+      <c r="E74" s="194" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="F74" s="195" t="inlineStr">
+      <c r="F74" s="194" t="inlineStr">
         <is>
           <t>L (1-5)</t>
         </is>
       </c>
-      <c r="G74" s="195" t="inlineStr">
+      <c r="G74" s="194" t="inlineStr">
         <is>
           <t>C (1-5)</t>
         </is>
       </c>
-      <c r="H74" s="195" t="inlineStr">
+      <c r="H74" s="194" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="I74" s="195" t="inlineStr">
+      <c r="I74" s="194" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="27.75" customHeight="1" s="132">
+    <row r="75" ht="27.75" customHeight="1" s="140">
       <c r="C75" s="72" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D75" s="210" t="inlineStr">
+      <c r="D75" s="215" t="inlineStr">
         <is>
           <t>Salt Supply Disruption (gangguan pasokan garam industri)</t>
         </is>
@@ -7454,7 +7451,7 @@
       <c r="G75" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="H75" s="188">
+      <c r="H75" s="149">
         <f>INDEX(Referensi_Threshold!$D$90:$D$114,MATCH(F75*10+G75,Referensi_Threshold!$A$90:$A$114,0))</f>
         <v/>
       </c>
@@ -7463,13 +7460,13 @@
         <v/>
       </c>
     </row>
-    <row r="76" ht="27.75" customHeight="1" s="132">
+    <row r="76" ht="27.75" customHeight="1" s="140">
       <c r="C76" s="72" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="D76" s="210" t="inlineStr">
+      <c r="D76" s="215" t="inlineStr">
         <is>
           <t>Commissioning Delay (keterlambatan commissioning)</t>
         </is>
@@ -7485,7 +7482,7 @@
       <c r="G76" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="H76" s="188">
+      <c r="H76" s="149">
         <f>INDEX(Referensi_Threshold!$D$90:$D$114,MATCH(F76*10+G76,Referensi_Threshold!$A$90:$A$114,0))</f>
         <v/>
       </c>
@@ -7494,13 +7491,13 @@
         <v/>
       </c>
     </row>
-    <row r="77" ht="27.75" customHeight="1" s="132">
+    <row r="77" ht="27.75" customHeight="1" s="140">
       <c r="C77" s="72" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D77" s="210" t="inlineStr">
+      <c r="D77" s="215" t="inlineStr">
         <is>
           <t>EPC Interface Issue (isu EPC interface lintas kontraktor)</t>
         </is>
@@ -7516,7 +7513,7 @@
       <c r="G77" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="H77" s="188">
+      <c r="H77" s="149">
         <f>INDEX(Referensi_Threshold!$D$90:$D$114,MATCH(F77*10+G77,Referensi_Threshold!$A$90:$A$114,0))</f>
         <v/>
       </c>
@@ -7525,13 +7522,13 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="23.25" customHeight="1" s="132">
+    <row r="78" ht="23.25" customHeight="1" s="140">
       <c r="C78" s="72" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D78" s="210" t="inlineStr">
+      <c r="D78" s="215" t="inlineStr">
         <is>
           <t>Long Lead Equipment (keterlambatan peralatan utama)</t>
         </is>
@@ -7547,7 +7544,7 @@
       <c r="G78" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="188">
+      <c r="H78" s="149">
         <f>INDEX(Referensi_Threshold!$D$90:$D$114,MATCH(F78*10+G78,Referensi_Threshold!$A$90:$A$114,0))</f>
         <v/>
       </c>
@@ -7588,32 +7585,32 @@
   <dimension ref="B2:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="2" customWidth="1" style="132" min="1" max="1"/>
-    <col width="26.53125" bestFit="1" customWidth="1" style="132" min="2" max="2"/>
-    <col width="26" customWidth="1" style="132" min="3" max="3"/>
-    <col width="18" customWidth="1" style="132" min="4" max="4"/>
-    <col width="38" customWidth="1" style="132" min="5" max="5"/>
-    <col width="24" customWidth="1" style="132" min="6" max="6"/>
-    <col width="36" customWidth="1" style="132" min="7" max="7"/>
-    <col width="25" customWidth="1" style="132" min="8" max="8"/>
-    <col width="17.265625" bestFit="1" customWidth="1" style="132" min="26" max="26"/>
+    <col width="2" customWidth="1" style="140" min="1" max="1"/>
+    <col width="26.53125" bestFit="1" customWidth="1" style="140" min="2" max="2"/>
+    <col width="26" customWidth="1" style="140" min="3" max="3"/>
+    <col width="18" customWidth="1" style="140" min="4" max="4"/>
+    <col width="38" customWidth="1" style="140" min="5" max="5"/>
+    <col width="24" customWidth="1" style="140" min="6" max="6"/>
+    <col width="36" customWidth="1" style="140" min="7" max="7"/>
+    <col width="25" customWidth="1" style="140" min="8" max="8"/>
+    <col width="17.265625" bestFit="1" customWidth="1" style="140" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="132">
-      <c r="B2" s="209" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1" s="140">
+      <c r="B2" s="214" t="inlineStr">
         <is>
           <t>EXECUTIVE ACTION TRACKER — DIREKSI / PROJECT STEERING COMMITTEE (PSC)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="132">
-      <c r="B3" s="133" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="140">
+      <c r="B3" s="201" t="inlineStr">
         <is>
           <t>Proyek X Project Perusahaan X — diperbarui setiap periode pelaporan bulanan. Kategori Level mengikuti klasifikasi 5-tingkat Pedoman Manajemen Risiko Perusahaan X.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="132">
+    <row r="5" ht="30" customHeight="1" s="140">
       <c r="B5" s="74" t="inlineStr">
         <is>
           <t>No</t>
@@ -7644,7 +7641,7 @@
           <t>Perkiraan Dampak Finansial &amp; Kelayakan NPV</t>
         </is>
       </c>
-      <c r="H5" s="214" t="inlineStr">
+      <c r="H5" s="130" t="inlineStr">
         <is>
           <t>Prioritas Dashboard (1, 2, 3...)</t>
         </is>
@@ -7655,7 +7652,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="73.5" customHeight="1" s="132">
+    <row r="6" ht="73.5" customHeight="1" s="140">
       <c r="B6" s="75" t="inlineStr">
         <is>
           <t>1</t>
@@ -7686,7 +7683,7 @@
           <t>Mencegah kegagalan penyelesaian proyek bersamaan, mengamankan target COD Maret 2028, melindungi NPV sebesar USD 77,60 Juta.</t>
         </is>
       </c>
-      <c r="H6" s="215" t="n">
+      <c r="H6" s="131" t="n">
         <v>1</v>
       </c>
       <c r="Z6" s="76">
@@ -7694,7 +7691,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="73.5" customHeight="1" s="132">
+    <row r="7" ht="73.5" customHeight="1" s="140">
       <c r="B7" s="75" t="inlineStr">
         <is>
           <t>2</t>
@@ -7725,7 +7722,7 @@
           <t>Melindungi penyelesaian gardu kelistrikan dan fasilitas tie-in, menghindari denda klaim tambahan dari EPC-A.</t>
         </is>
       </c>
-      <c r="H7" s="215" t="n">
+      <c r="H7" s="131" t="n">
         <v>2</v>
       </c>
       <c r="Z7" s="76">
@@ -7733,7 +7730,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="73.5" customHeight="1" s="132">
+    <row r="8" ht="73.5" customHeight="1" s="140">
       <c r="B8" s="75" t="inlineStr">
         <is>
           <t>3</t>
@@ -7764,7 +7761,7 @@
           <t>Menghindari penghentian operasional akibat kekosongan bahan baku; menghemat potensi kerugian EBITDA Rp 137 Miliar/kuartal.</t>
         </is>
       </c>
-      <c r="H8" s="215" t="n">
+      <c r="H8" s="131" t="n">
         <v>3</v>
       </c>
       <c r="Z8" s="76">
@@ -7772,7 +7769,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="73.5" customHeight="1" s="132">
+    <row r="9" ht="73.5" customHeight="1" s="140">
       <c r="B9" s="75" t="inlineStr">
         <is>
           <t>4</t>
@@ -7803,7 +7800,7 @@
           <t>Mengeliminasi risiko pembengkakan biaya investasi riil akibat depresiasi rupiah; mengamankan ambang batas investasi USD 297,67 Juta.</t>
         </is>
       </c>
-      <c r="H9" s="215" t="n">
+      <c r="H9" s="131" t="n">
         <v>4</v>
       </c>
       <c r="Z9" s="76">
@@ -7811,7 +7808,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="73.5" customHeight="1" s="132">
+    <row r="10" ht="73.5" customHeight="1" s="140">
       <c r="B10" s="75" t="inlineStr">
         <is>
           <t>5</t>
@@ -7842,7 +7839,7 @@
           <t>Mencegah keterlambatan masa efektif konstruksi fisik; menghemat opportunity cost of capital senilai Rp 500 Juta/bulan.</t>
         </is>
       </c>
-      <c r="H10" s="215" t="n">
+      <c r="H10" s="131" t="n">
         <v>5</v>
       </c>
       <c r="Z10" s="76">
@@ -7856,8 +7853,8 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="132">
-      <c r="B12" s="212" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="140">
+      <c r="B12" s="217" t="inlineStr">
         <is>
           <t>Sumber tata kelola: Risk Register Proyek X 2025; kerangka Gate Review &amp; FID PT Pertamina (Persero); Weighted Project Top Risk (Financial Materiality 40%, Strategic Impact 30%, Life Cycle Phase 15%, Financial Health Impact 10%, Baseline Risk Complexity 5%). Level risiko mengikuti klasifikasi 5-tingkat Pedoman Manajemen Risiko Perusahaan X: Low / Low to Moderate / Moderate / Moderate to High / High.</t>
         </is>
@@ -7867,13 +7864,13 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="132">
+    <row r="13" ht="15" customHeight="1" s="140">
       <c r="Z13" s="111">
         <f>IF(D13="","", IF(ISNUMBER(SEARCH("Moderate to High", D13)), 40, IF(ISNUMBER(SEARCH("High", D13)), 50, IF(ISNUMBER(SEARCH("Low to Moderate", D13)), 20, IF(ISNUMBER(SEARCH("Moderate", D13)), 30, 10)))) + (1/ROW()))</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="132">
+    <row r="14" ht="15" customHeight="1" s="140">
       <c r="Z14" s="111">
         <f>IF(D14="","", IF(ISNUMBER(SEARCH("Moderate to High", D14)), 40, IF(ISNUMBER(SEARCH("High", D14)), 50, IF(ISNUMBER(SEARCH("Low to Moderate", D14)), 20, IF(ISNUMBER(SEARCH("Moderate", D14)), 30, 10)))) + (1/ROW()))</f>
         <v/>
@@ -7885,14 +7882,14 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="132">
-      <c r="B16" s="211" t="inlineStr">
+    <row r="16" ht="18" customHeight="1" s="140">
+      <c r="B16" s="216" t="inlineStr">
         <is>
           <t>DINAMIKA PERGERAKAN RISIKO (BULAN BERJALAN)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="27.75" customHeight="1" s="132">
+    <row r="17" ht="27.75" customHeight="1" s="140">
       <c r="B17" s="80" t="inlineStr">
         <is>
           <t>Risiko Baru (New Risk)</t>
@@ -7902,16 +7899,16 @@
         <f>Input_Bulanan!F60</f>
         <v/>
       </c>
-      <c r="D17" s="210" t="inlineStr">
+      <c r="D17" s="215" t="inlineStr">
         <is>
           <t>Perubahan tarif pajak masukan impor garam industri; risiko sengketa lahan tambahan di area laydown.</t>
         </is>
       </c>
-      <c r="E17" s="142" t="n"/>
-      <c r="F17" s="142" t="n"/>
-      <c r="G17" s="143" t="n"/>
-    </row>
-    <row r="18" ht="27.75" customHeight="1" s="132">
+      <c r="E17" s="136" t="n"/>
+      <c r="F17" s="136" t="n"/>
+      <c r="G17" s="137" t="n"/>
+    </row>
+    <row r="18" ht="27.75" customHeight="1" s="140">
       <c r="B18" s="80" t="inlineStr">
         <is>
           <t>Risiko Eskalasi (Escalated Risk)</t>
@@ -7921,16 +7918,16 @@
         <f>Input_Bulanan!F61</f>
         <v/>
       </c>
-      <c r="D18" s="210" t="inlineStr">
+      <c r="D18" s="215" t="inlineStr">
         <is>
           <t>Peningkatan level risiko keterlambatan Rekind akibat kendala arus kas internal.</t>
         </is>
       </c>
-      <c r="E18" s="142" t="n"/>
-      <c r="F18" s="142" t="n"/>
-      <c r="G18" s="143" t="n"/>
-    </row>
-    <row r="19" ht="27.75" customHeight="1" s="132">
+      <c r="E18" s="136" t="n"/>
+      <c r="F18" s="136" t="n"/>
+      <c r="G18" s="137" t="n"/>
+    </row>
+    <row r="19" ht="27.75" customHeight="1" s="140">
       <c r="B19" s="80" t="inlineStr">
         <is>
           <t>Risiko Menurun (Reduced Risk)</t>
@@ -7940,16 +7937,16 @@
         <f>Input_Bulanan!F62</f>
         <v/>
       </c>
-      <c r="D19" s="210" t="inlineStr">
+      <c r="D19" s="215" t="inlineStr">
         <is>
           <t>Penurunan risiko dampak sosial setelah disepakatinya kuota tenaga kerja lokal.</t>
         </is>
       </c>
-      <c r="E19" s="142" t="n"/>
-      <c r="F19" s="142" t="n"/>
-      <c r="G19" s="143" t="n"/>
-    </row>
-    <row r="20" ht="27.75" customHeight="1" s="132">
+      <c r="E19" s="136" t="n"/>
+      <c r="F19" s="136" t="n"/>
+      <c r="G19" s="137" t="n"/>
+    </row>
+    <row r="20" ht="27.75" customHeight="1" s="140">
       <c r="B20" s="80" t="inlineStr">
         <is>
           <t>Risiko Ditutup (Closed Risk)</t>
@@ -7959,60 +7956,60 @@
         <f>Input_Bulanan!F63</f>
         <v/>
       </c>
-      <c r="D20" s="210" t="inlineStr">
+      <c r="D20" s="215" t="inlineStr">
         <is>
           <t>Penutupan risiko kelayakan AMDAL seiring diterbitkannya izin adendum lingkungan DLH Bontang.</t>
         </is>
       </c>
-      <c r="E20" s="142" t="n"/>
-      <c r="F20" s="142" t="n"/>
-      <c r="G20" s="143" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" s="132">
-      <c r="B22" s="211" t="inlineStr">
+      <c r="E20" s="136" t="n"/>
+      <c r="F20" s="136" t="n"/>
+      <c r="G20" s="137" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="140">
+      <c r="B22" s="216" t="inlineStr">
         <is>
           <t>TOP RISK REGISTER (C1-C4) - DETAIL LIKELIHOOD x CONSEQUENCE</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="132">
-      <c r="B23" s="152" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="140">
+      <c r="B23" s="164" t="inlineStr">
         <is>
           <t>Kode</t>
         </is>
       </c>
-      <c r="C23" s="152" t="inlineStr">
+      <c r="C23" s="164" t="inlineStr">
         <is>
           <t>Deskripsi Risiko</t>
         </is>
       </c>
-      <c r="D23" s="152" t="inlineStr">
+      <c r="D23" s="164" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="E23" s="152" t="inlineStr">
+      <c r="E23" s="164" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F23" s="152" t="inlineStr">
+      <c r="F23" s="164" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G23" s="152" t="inlineStr">
+      <c r="G23" s="164" t="inlineStr">
         <is>
           <t>Score / Level</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="25.5" customHeight="1" s="132">
+    <row r="24" ht="25.5" customHeight="1" s="140">
       <c r="B24" s="72">
         <f>Input_Bulanan!C75</f>
         <v/>
       </c>
-      <c r="C24" s="210">
+      <c r="C24" s="215">
         <f>Input_Bulanan!D75</f>
         <v/>
       </c>
@@ -8033,12 +8030,12 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="25.5" customHeight="1" s="132">
+    <row r="25" ht="25.5" customHeight="1" s="140">
       <c r="B25" s="72">
         <f>Input_Bulanan!C76</f>
         <v/>
       </c>
-      <c r="C25" s="210">
+      <c r="C25" s="215">
         <f>Input_Bulanan!D76</f>
         <v/>
       </c>
@@ -8059,12 +8056,12 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="25.5" customHeight="1" s="132">
+    <row r="26" ht="25.5" customHeight="1" s="140">
       <c r="B26" s="72">
         <f>Input_Bulanan!C77</f>
         <v/>
       </c>
-      <c r="C26" s="210">
+      <c r="C26" s="215">
         <f>Input_Bulanan!D77</f>
         <v/>
       </c>
@@ -8085,12 +8082,12 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="25.5" customHeight="1" s="132">
+    <row r="27" ht="25.5" customHeight="1" s="140">
       <c r="B27" s="72">
         <f>Input_Bulanan!C78</f>
         <v/>
       </c>
-      <c r="C27" s="210">
+      <c r="C27" s="215">
         <f>Input_Bulanan!D78</f>
         <v/>
       </c>
